--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>91724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R10" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B11" t="n">
-        <v>91724</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R11" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330860</v>
+        <v>130330831</v>
       </c>
       <c r="B4" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444738</v>
+        <v>444731</v>
       </c>
       <c r="R4" t="n">
-        <v>7025522</v>
+        <v>7025453</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330831</v>
+        <v>130330860</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444731</v>
+        <v>444738</v>
       </c>
       <c r="R5" t="n">
-        <v>7025453</v>
+        <v>7025522</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B10" t="n">
-        <v>91724</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R10" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>91724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R11" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3808,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330845</v>
+        <v>130330822</v>
       </c>
       <c r="B30" t="n">
-        <v>83163</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444588</v>
+        <v>444629</v>
       </c>
       <c r="R30" t="n">
-        <v>7025517</v>
+        <v>7025390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330822</v>
+        <v>130330845</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>83163</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444629</v>
+        <v>444588</v>
       </c>
       <c r="R31" t="n">
-        <v>7025390</v>
+        <v>7025517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130330846</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330856</v>
+        <v>130330860</v>
       </c>
       <c r="B3" t="n">
-        <v>80286</v>
+        <v>80288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444718</v>
+        <v>444738</v>
       </c>
       <c r="R3" t="n">
-        <v>7025527</v>
+        <v>7025522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330831</v>
+        <v>130330856</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>80289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444731</v>
+        <v>444718</v>
       </c>
       <c r="R4" t="n">
-        <v>7025453</v>
+        <v>7025527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330860</v>
+        <v>130330831</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444738</v>
+        <v>444731</v>
       </c>
       <c r="R5" t="n">
-        <v>7025522</v>
+        <v>7025453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130330824</v>
+        <v>130330857</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444645</v>
+        <v>444718</v>
       </c>
       <c r="R6" t="n">
-        <v>7025385</v>
+        <v>7025527</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130330857</v>
+        <v>130330824</v>
       </c>
       <c r="B7" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444718</v>
+        <v>444645</v>
       </c>
       <c r="R7" t="n">
-        <v>7025527</v>
+        <v>7025385</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1350,7 @@
         <v>130330836</v>
       </c>
       <c r="B8" t="n">
-        <v>80314</v>
+        <v>80317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130330828</v>
       </c>
       <c r="B9" t="n">
-        <v>80321</v>
+        <v>80324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>91727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R10" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B11" t="n">
-        <v>91724</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R11" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,7 +1798,7 @@
         <v>130330843</v>
       </c>
       <c r="B12" t="n">
-        <v>75158</v>
+        <v>75161</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130330830</v>
       </c>
       <c r="B13" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>130330835</v>
       </c>
       <c r="B14" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>130330837</v>
       </c>
       <c r="B15" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,45 +2243,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130330823</v>
+        <v>130330858</v>
       </c>
       <c r="B16" t="n">
-        <v>97791</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444645</v>
+        <v>444728</v>
       </c>
       <c r="R16" t="n">
-        <v>7025385</v>
+        <v>7025532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,12 +2332,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på marken i gammal granskog</t>
+          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130330858</v>
+        <v>130330839</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,26 +2392,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444728</v>
+        <v>444650</v>
       </c>
       <c r="R17" t="n">
-        <v>7025532</v>
+        <v>7025524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
+          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130330839</v>
+        <v>130330840</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444650</v>
+        <v>444637</v>
       </c>
       <c r="R18" t="n">
-        <v>7025524</v>
+        <v>7025502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
+          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130330840</v>
+        <v>130330823</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>97794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444637</v>
+        <v>444645</v>
       </c>
       <c r="R19" t="n">
-        <v>7025502</v>
+        <v>7025385</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,7 +2703,7 @@
         <v>130330826</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>130330825</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>130330841</v>
       </c>
       <c r="B22" t="n">
-        <v>78192</v>
+        <v>78195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>130330854</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>130330842</v>
       </c>
       <c r="B24" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>130330851</v>
       </c>
       <c r="B25" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130330833</v>
+        <v>130330827</v>
       </c>
       <c r="B26" t="n">
-        <v>80189</v>
+        <v>80288</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444731</v>
+        <v>444727</v>
       </c>
       <c r="R26" t="n">
-        <v>7025453</v>
+        <v>7025514</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>rikligt på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,32 +3476,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130330827</v>
+        <v>130330833</v>
       </c>
       <c r="B27" t="n">
-        <v>80285</v>
+        <v>80192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444727</v>
+        <v>444731</v>
       </c>
       <c r="R27" t="n">
-        <v>7025514</v>
+        <v>7025453</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande sälg i gammal granskog</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,7 +3591,7 @@
         <v>130330847</v>
       </c>
       <c r="B28" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>130330848</v>
       </c>
       <c r="B29" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>130330822</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>130330845</v>
       </c>
       <c r="B31" t="n">
-        <v>83163</v>
+        <v>83166</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>130330859</v>
       </c>
       <c r="B32" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>130330838</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>130330849</v>
       </c>
       <c r="B34" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330855</v>
+        <v>130330850</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>83161</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,43 +4375,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444696</v>
+        <v>444566</v>
       </c>
       <c r="R35" t="n">
-        <v>7025558</v>
+        <v>7025535</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4443,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4453,12 +4444,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4485,10 +4476,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330850</v>
+        <v>130330855</v>
       </c>
       <c r="B36" t="n">
-        <v>83158</v>
+        <v>79183</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,34 +4487,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444566</v>
+        <v>444696</v>
       </c>
       <c r="R36" t="n">
-        <v>7025535</v>
+        <v>7025558</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4597,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130330832</v>
+        <v>130330829</v>
       </c>
       <c r="B37" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>på två gamla sälgar i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130330846</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330860</v>
+        <v>130330856</v>
       </c>
       <c r="B3" t="n">
-        <v>80288</v>
+        <v>80315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444738</v>
+        <v>444718</v>
       </c>
       <c r="R3" t="n">
-        <v>7025522</v>
+        <v>7025527</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330856</v>
+        <v>130330831</v>
       </c>
       <c r="B4" t="n">
-        <v>80289</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444718</v>
+        <v>444731</v>
       </c>
       <c r="R4" t="n">
-        <v>7025527</v>
+        <v>7025453</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330831</v>
+        <v>130330860</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>80314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444731</v>
+        <v>444738</v>
       </c>
       <c r="R5" t="n">
-        <v>7025453</v>
+        <v>7025522</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>130330857</v>
       </c>
       <c r="B6" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130330824</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130330836</v>
       </c>
       <c r="B8" t="n">
-        <v>80317</v>
+        <v>80343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130330828</v>
       </c>
       <c r="B9" t="n">
-        <v>80324</v>
+        <v>80350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>130330852</v>
       </c>
       <c r="B10" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130330834</v>
       </c>
       <c r="B11" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130330843</v>
       </c>
       <c r="B12" t="n">
-        <v>75161</v>
+        <v>75187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130330830</v>
       </c>
       <c r="B13" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330835</v>
+        <v>130330837</v>
       </c>
       <c r="B14" t="n">
-        <v>80289</v>
+        <v>80314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B15" t="n">
-        <v>80288</v>
+        <v>80315</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
         <v>130330858</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>130330839</v>
       </c>
       <c r="B17" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>130330840</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>130330823</v>
       </c>
       <c r="B19" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>130330826</v>
       </c>
       <c r="B20" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>130330825</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>130330841</v>
       </c>
       <c r="B22" t="n">
-        <v>78195</v>
+        <v>78221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>130330854</v>
       </c>
       <c r="B23" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>130330842</v>
       </c>
       <c r="B24" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>130330851</v>
       </c>
       <c r="B25" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130330827</v>
+        <v>130330833</v>
       </c>
       <c r="B26" t="n">
-        <v>80288</v>
+        <v>80218</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444727</v>
+        <v>444731</v>
       </c>
       <c r="R26" t="n">
-        <v>7025514</v>
+        <v>7025453</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande sälg i gammal granskog</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,32 +3476,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130330833</v>
+        <v>130330827</v>
       </c>
       <c r="B27" t="n">
-        <v>80192</v>
+        <v>80314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444731</v>
+        <v>444727</v>
       </c>
       <c r="R27" t="n">
-        <v>7025453</v>
+        <v>7025514</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>rikligt på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,7 +3591,7 @@
         <v>130330847</v>
       </c>
       <c r="B28" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>130330848</v>
       </c>
       <c r="B29" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330822</v>
+        <v>130330845</v>
       </c>
       <c r="B30" t="n">
-        <v>79183</v>
+        <v>83192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444629</v>
+        <v>444588</v>
       </c>
       <c r="R30" t="n">
-        <v>7025390</v>
+        <v>7025517</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330845</v>
+        <v>130330822</v>
       </c>
       <c r="B31" t="n">
-        <v>83166</v>
+        <v>79209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444588</v>
+        <v>444629</v>
       </c>
       <c r="R31" t="n">
-        <v>7025517</v>
+        <v>7025390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4032,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330859</v>
+        <v>130330838</v>
       </c>
       <c r="B32" t="n">
-        <v>80289</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444738</v>
+        <v>444683</v>
       </c>
       <c r="R32" t="n">
-        <v>7025522</v>
+        <v>7025492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330838</v>
+        <v>130330859</v>
       </c>
       <c r="B33" t="n">
-        <v>79183</v>
+        <v>80315</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444683</v>
+        <v>444738</v>
       </c>
       <c r="R33" t="n">
-        <v>7025492</v>
+        <v>7025522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330849</v>
+        <v>130330850</v>
       </c>
       <c r="B34" t="n">
-        <v>91751</v>
+        <v>83187</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,19 +4267,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4287,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444569</v>
+        <v>444566</v>
       </c>
       <c r="R34" t="n">
-        <v>7025541</v>
+        <v>7025535</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,12 +4336,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på grov granhögstubbe i gammal granskog nära dike</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,10 +4368,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330850</v>
+        <v>130330849</v>
       </c>
       <c r="B35" t="n">
-        <v>83161</v>
+        <v>91777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,23 +4379,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444566</v>
+        <v>444569</v>
       </c>
       <c r="R35" t="n">
-        <v>7025535</v>
+        <v>7025541</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på grov granhögstubbe i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4479,7 +4479,7 @@
         <v>130330855</v>
       </c>
       <c r="B36" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130330829</v>
+        <v>130330832</v>
       </c>
       <c r="B37" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på två gamla sälgar i gammal barrblandskog</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -2243,54 +2243,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130330858</v>
+        <v>130330823</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>97820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444728</v>
+        <v>444645</v>
       </c>
       <c r="R16" t="n">
-        <v>7025532</v>
+        <v>7025385</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,12 +2323,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
+          <t>på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130330839</v>
+        <v>130330858</v>
       </c>
       <c r="B17" t="n">
         <v>79209</v>
@@ -2392,17 +2383,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444650</v>
+        <v>444728</v>
       </c>
       <c r="R17" t="n">
-        <v>7025524</v>
+        <v>7025532</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
+          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,7 +2476,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130330840</v>
+        <v>130330839</v>
       </c>
       <c r="B18" t="n">
         <v>79209</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444637</v>
+        <v>444650</v>
       </c>
       <c r="R18" t="n">
-        <v>7025502</v>
+        <v>7025524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130330823</v>
+        <v>130330840</v>
       </c>
       <c r="B19" t="n">
-        <v>97820</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444645</v>
+        <v>444637</v>
       </c>
       <c r="R19" t="n">
-        <v>7025385</v>
+        <v>7025502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på marken i gammal granskog</t>
+          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3148,30 +3148,34 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130330842</v>
+        <v>130330833</v>
       </c>
       <c r="B24" t="n">
-        <v>91777</v>
+        <v>80218</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3179,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444550</v>
+        <v>444731</v>
       </c>
       <c r="R24" t="n">
-        <v>7025500</v>
+        <v>7025453</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,12 +3228,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130330851</v>
+        <v>130330827</v>
       </c>
       <c r="B25" t="n">
-        <v>91777</v>
+        <v>80314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,19 +3271,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3287,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444607</v>
+        <v>444727</v>
       </c>
       <c r="R25" t="n">
-        <v>7025579</v>
+        <v>7025514</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3322,7 +3330,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3332,12 +3340,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>på död stående gran vid dike/bäck</t>
+          <t>rikligt på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,34 +3372,30 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130330833</v>
+        <v>130330842</v>
       </c>
       <c r="B26" t="n">
-        <v>80218</v>
+        <v>91777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3399,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444731</v>
+        <v>444550</v>
       </c>
       <c r="R26" t="n">
-        <v>7025453</v>
+        <v>7025500</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,12 +3448,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130330827</v>
+        <v>130330851</v>
       </c>
       <c r="B27" t="n">
-        <v>80314</v>
+        <v>91777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3487,23 +3491,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444727</v>
+        <v>444607</v>
       </c>
       <c r="R27" t="n">
-        <v>7025514</v>
+        <v>7025579</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande sälg i gammal granskog</t>
+          <t>på död stående gran vid dike/bäck</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330850</v>
+        <v>130330849</v>
       </c>
       <c r="B34" t="n">
-        <v>83187</v>
+        <v>91777</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,23 +4267,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4291,10 +4287,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444566</v>
+        <v>444569</v>
       </c>
       <c r="R34" t="n">
-        <v>7025535</v>
+        <v>7025541</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4326,7 +4322,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,12 +4332,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på grov granhögstubbe i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4368,10 +4364,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330849</v>
+        <v>130330855</v>
       </c>
       <c r="B35" t="n">
-        <v>91777</v>
+        <v>79209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,30 +4375,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444569</v>
+        <v>444696</v>
       </c>
       <c r="R35" t="n">
-        <v>7025541</v>
+        <v>7025558</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4434,7 +4443,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,12 +4453,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på grov granhögstubbe i gammal granskog nära dike</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4476,10 +4485,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330855</v>
+        <v>130330850</v>
       </c>
       <c r="B36" t="n">
-        <v>79209</v>
+        <v>83187</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4487,43 +4496,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444696</v>
+        <v>444566</v>
       </c>
       <c r="R36" t="n">
-        <v>7025558</v>
+        <v>7025535</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>130330852</v>
       </c>
       <c r="B10" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B14" t="n">
-        <v>80314</v>
+        <v>80315</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330835</v>
+        <v>130330837</v>
       </c>
       <c r="B15" t="n">
-        <v>80315</v>
+        <v>80314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2243,45 +2243,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130330823</v>
+        <v>130330858</v>
       </c>
       <c r="B16" t="n">
-        <v>97820</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444645</v>
+        <v>444728</v>
       </c>
       <c r="R16" t="n">
-        <v>7025385</v>
+        <v>7025532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,12 +2332,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på marken i gammal granskog</t>
+          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,7 +2364,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130330858</v>
+        <v>130330839</v>
       </c>
       <c r="B17" t="n">
         <v>79209</v>
@@ -2383,26 +2392,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444728</v>
+        <v>444650</v>
       </c>
       <c r="R17" t="n">
-        <v>7025532</v>
+        <v>7025524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
+          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,7 +2476,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130330839</v>
+        <v>130330840</v>
       </c>
       <c r="B18" t="n">
         <v>79209</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444650</v>
+        <v>444637</v>
       </c>
       <c r="R18" t="n">
-        <v>7025524</v>
+        <v>7025502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
+          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130330840</v>
+        <v>130330823</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>97821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444637</v>
+        <v>444645</v>
       </c>
       <c r="R19" t="n">
-        <v>7025502</v>
+        <v>7025385</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3148,34 +3148,30 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130330833</v>
+        <v>130330842</v>
       </c>
       <c r="B24" t="n">
-        <v>80218</v>
+        <v>91778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3183,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444731</v>
+        <v>444550</v>
       </c>
       <c r="R24" t="n">
-        <v>7025453</v>
+        <v>7025500</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3218,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,12 +3224,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130330827</v>
+        <v>130330851</v>
       </c>
       <c r="B25" t="n">
-        <v>80314</v>
+        <v>91778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,23 +3267,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3295,10 +3287,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444727</v>
+        <v>444607</v>
       </c>
       <c r="R25" t="n">
-        <v>7025514</v>
+        <v>7025579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3330,7 +3322,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3340,12 +3332,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande sälg i gammal granskog</t>
+          <t>på död stående gran vid dike/bäck</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,30 +3364,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130330842</v>
+        <v>130330833</v>
       </c>
       <c r="B26" t="n">
-        <v>91777</v>
+        <v>80218</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3403,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444550</v>
+        <v>444731</v>
       </c>
       <c r="R26" t="n">
-        <v>7025500</v>
+        <v>7025453</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3438,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,12 +3444,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,10 +3476,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130330851</v>
+        <v>130330827</v>
       </c>
       <c r="B27" t="n">
-        <v>91777</v>
+        <v>80314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,19 +3487,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444607</v>
+        <v>444727</v>
       </c>
       <c r="R27" t="n">
-        <v>7025579</v>
+        <v>7025514</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på död stående gran vid dike/bäck</t>
+          <t>rikligt på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,7 +3591,7 @@
         <v>130330847</v>
       </c>
       <c r="B28" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>130330848</v>
       </c>
       <c r="B29" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>130330845</v>
       </c>
       <c r="B30" t="n">
-        <v>83192</v>
+        <v>83193</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330838</v>
+        <v>130330859</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>80315</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444683</v>
+        <v>444738</v>
       </c>
       <c r="R32" t="n">
-        <v>7025492</v>
+        <v>7025522</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330859</v>
+        <v>130330838</v>
       </c>
       <c r="B33" t="n">
-        <v>80315</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444738</v>
+        <v>444683</v>
       </c>
       <c r="R33" t="n">
-        <v>7025522</v>
+        <v>7025492</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,7 +4259,7 @@
         <v>130330849</v>
       </c>
       <c r="B34" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>130330850</v>
       </c>
       <c r="B36" t="n">
-        <v>83187</v>
+        <v>83188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330831</v>
+        <v>130330860</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444731</v>
+        <v>444738</v>
       </c>
       <c r="R4" t="n">
-        <v>7025453</v>
+        <v>7025522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330860</v>
+        <v>130330831</v>
       </c>
       <c r="B5" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444738</v>
+        <v>444731</v>
       </c>
       <c r="R5" t="n">
-        <v>7025522</v>
+        <v>7025453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B10" t="n">
-        <v>91754</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R10" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>91755</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R11" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2591,7 +2591,7 @@
         <v>130330823</v>
       </c>
       <c r="B19" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130330826</v>
+        <v>130330825</v>
       </c>
       <c r="B20" t="n">
         <v>79209</v>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444727</v>
+        <v>444715</v>
       </c>
       <c r="R20" t="n">
-        <v>7025514</v>
+        <v>7025456</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2812,7 +2812,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130330825</v>
+        <v>130330826</v>
       </c>
       <c r="B21" t="n">
         <v>79209</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444715</v>
+        <v>444727</v>
       </c>
       <c r="R21" t="n">
-        <v>7025456</v>
+        <v>7025514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3151,7 +3151,7 @@
         <v>130330842</v>
       </c>
       <c r="B24" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>130330851</v>
       </c>
       <c r="B25" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>130330847</v>
       </c>
       <c r="B28" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>130330848</v>
       </c>
       <c r="B29" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>130330845</v>
       </c>
       <c r="B30" t="n">
-        <v>83193</v>
+        <v>83194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330859</v>
+        <v>130330838</v>
       </c>
       <c r="B32" t="n">
-        <v>80315</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444738</v>
+        <v>444683</v>
       </c>
       <c r="R32" t="n">
-        <v>7025522</v>
+        <v>7025492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330838</v>
+        <v>130330859</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>80315</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444683</v>
+        <v>444738</v>
       </c>
       <c r="R33" t="n">
-        <v>7025492</v>
+        <v>7025522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,7 +4259,7 @@
         <v>130330849</v>
       </c>
       <c r="B34" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330855</v>
+        <v>130330850</v>
       </c>
       <c r="B35" t="n">
-        <v>79209</v>
+        <v>83189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,43 +4375,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444696</v>
+        <v>444566</v>
       </c>
       <c r="R35" t="n">
-        <v>7025558</v>
+        <v>7025535</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4443,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4453,12 +4444,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4485,10 +4476,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330850</v>
+        <v>130330855</v>
       </c>
       <c r="B36" t="n">
-        <v>83188</v>
+        <v>79209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,34 +4487,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444566</v>
+        <v>444696</v>
       </c>
       <c r="R36" t="n">
-        <v>7025535</v>
+        <v>7025558</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130330846</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130330856</v>
       </c>
       <c r="B3" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130330860</v>
       </c>
       <c r="B4" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130330831</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130330857</v>
+        <v>130330824</v>
       </c>
       <c r="B6" t="n">
-        <v>80314</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444718</v>
+        <v>444645</v>
       </c>
       <c r="R6" t="n">
-        <v>7025527</v>
+        <v>7025385</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130330824</v>
+        <v>130330857</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>80316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444645</v>
+        <v>444718</v>
       </c>
       <c r="R7" t="n">
-        <v>7025385</v>
+        <v>7025527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1350,7 @@
         <v>130330836</v>
       </c>
       <c r="B8" t="n">
-        <v>80343</v>
+        <v>80345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130330828</v>
       </c>
       <c r="B9" t="n">
-        <v>80350</v>
+        <v>80352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>91757</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R10" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B11" t="n">
-        <v>91755</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R11" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,7 +1798,7 @@
         <v>130330843</v>
       </c>
       <c r="B12" t="n">
-        <v>75187</v>
+        <v>75189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130330830</v>
       </c>
       <c r="B13" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330835</v>
+        <v>130330837</v>
       </c>
       <c r="B14" t="n">
-        <v>80315</v>
+        <v>80316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B15" t="n">
-        <v>80314</v>
+        <v>80317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2243,54 +2243,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130330858</v>
+        <v>130330823</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>97824</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444728</v>
+        <v>444645</v>
       </c>
       <c r="R16" t="n">
-        <v>7025532</v>
+        <v>7025385</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,12 +2323,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
+          <t>på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130330839</v>
+        <v>130330858</v>
       </c>
       <c r="B17" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,17 +2383,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444650</v>
+        <v>444728</v>
       </c>
       <c r="R17" t="n">
-        <v>7025524</v>
+        <v>7025532</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
+          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130330840</v>
+        <v>130330839</v>
       </c>
       <c r="B18" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444637</v>
+        <v>444650</v>
       </c>
       <c r="R18" t="n">
-        <v>7025502</v>
+        <v>7025524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130330823</v>
+        <v>130330840</v>
       </c>
       <c r="B19" t="n">
-        <v>97822</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444645</v>
+        <v>444637</v>
       </c>
       <c r="R19" t="n">
-        <v>7025385</v>
+        <v>7025502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på marken i gammal granskog</t>
+          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130330825</v>
+        <v>130330841</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>78223</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,21 +2711,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444715</v>
+        <v>444637</v>
       </c>
       <c r="R20" t="n">
-        <v>7025456</v>
+        <v>7025502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2815,7 +2815,7 @@
         <v>130330826</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130330841</v>
+        <v>130330825</v>
       </c>
       <c r="B22" t="n">
-        <v>78221</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444637</v>
+        <v>444715</v>
       </c>
       <c r="R22" t="n">
-        <v>7025502</v>
+        <v>7025456</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3039,7 +3039,7 @@
         <v>130330854</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>130330842</v>
       </c>
       <c r="B24" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>130330851</v>
       </c>
       <c r="B25" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>130330833</v>
       </c>
       <c r="B26" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>130330827</v>
       </c>
       <c r="B27" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>130330847</v>
       </c>
       <c r="B28" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>130330848</v>
       </c>
       <c r="B29" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330845</v>
+        <v>130330822</v>
       </c>
       <c r="B30" t="n">
-        <v>83194</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444588</v>
+        <v>444629</v>
       </c>
       <c r="R30" t="n">
-        <v>7025517</v>
+        <v>7025390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330822</v>
+        <v>130330845</v>
       </c>
       <c r="B31" t="n">
-        <v>79209</v>
+        <v>83196</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444629</v>
+        <v>444588</v>
       </c>
       <c r="R31" t="n">
-        <v>7025390</v>
+        <v>7025517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,7 +4035,7 @@
         <v>130330838</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>130330859</v>
       </c>
       <c r="B33" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>130330849</v>
       </c>
       <c r="B34" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330850</v>
+        <v>130330855</v>
       </c>
       <c r="B35" t="n">
-        <v>83189</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,34 +4375,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444566</v>
+        <v>444696</v>
       </c>
       <c r="R35" t="n">
-        <v>7025535</v>
+        <v>7025558</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4434,7 +4443,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,12 +4453,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4476,10 +4485,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330855</v>
+        <v>130330850</v>
       </c>
       <c r="B36" t="n">
-        <v>79209</v>
+        <v>83191</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4487,43 +4496,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444696</v>
+        <v>444566</v>
       </c>
       <c r="R36" t="n">
-        <v>7025558</v>
+        <v>7025535</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4600,7 +4600,7 @@
         <v>130330832</v>
       </c>
       <c r="B37" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330856</v>
+        <v>130330831</v>
       </c>
       <c r="B3" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444718</v>
+        <v>444731</v>
       </c>
       <c r="R3" t="n">
-        <v>7025527</v>
+        <v>7025453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330831</v>
+        <v>130330856</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>80317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444731</v>
+        <v>444718</v>
       </c>
       <c r="R5" t="n">
-        <v>7025453</v>
+        <v>7025527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130330824</v>
+        <v>130330857</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444645</v>
+        <v>444718</v>
       </c>
       <c r="R6" t="n">
-        <v>7025385</v>
+        <v>7025527</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130330857</v>
+        <v>130330824</v>
       </c>
       <c r="B7" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444718</v>
+        <v>444645</v>
       </c>
       <c r="R7" t="n">
-        <v>7025527</v>
+        <v>7025385</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B14" t="n">
-        <v>80316</v>
+        <v>80317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330835</v>
+        <v>130330837</v>
       </c>
       <c r="B15" t="n">
-        <v>80317</v>
+        <v>80316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
         <v>130330823</v>
       </c>
       <c r="B16" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130330841</v>
+        <v>130330826</v>
       </c>
       <c r="B20" t="n">
-        <v>78223</v>
+        <v>79211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,21 +2711,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444637</v>
+        <v>444727</v>
       </c>
       <c r="R20" t="n">
-        <v>7025502</v>
+        <v>7025514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,7 +2812,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130330826</v>
+        <v>130330825</v>
       </c>
       <c r="B21" t="n">
         <v>79211</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444727</v>
+        <v>444715</v>
       </c>
       <c r="R21" t="n">
-        <v>7025514</v>
+        <v>7025456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130330825</v>
+        <v>130330841</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>78223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444715</v>
+        <v>444637</v>
       </c>
       <c r="R22" t="n">
-        <v>7025456</v>
+        <v>7025502</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3148,30 +3148,34 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130330842</v>
+        <v>130330833</v>
       </c>
       <c r="B24" t="n">
-        <v>91781</v>
+        <v>80220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3179,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444550</v>
+        <v>444731</v>
       </c>
       <c r="R24" t="n">
-        <v>7025500</v>
+        <v>7025453</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,12 +3228,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130330851</v>
+        <v>130330827</v>
       </c>
       <c r="B25" t="n">
-        <v>91781</v>
+        <v>80316</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,19 +3271,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3287,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444607</v>
+        <v>444727</v>
       </c>
       <c r="R25" t="n">
-        <v>7025579</v>
+        <v>7025514</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3322,7 +3330,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3332,12 +3340,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>på död stående gran vid dike/bäck</t>
+          <t>rikligt på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,34 +3372,30 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130330833</v>
+        <v>130330851</v>
       </c>
       <c r="B26" t="n">
-        <v>80220</v>
+        <v>91781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3399,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444731</v>
+        <v>444607</v>
       </c>
       <c r="R26" t="n">
-        <v>7025453</v>
+        <v>7025579</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,12 +3448,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>på död stående gran vid dike/bäck</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130330827</v>
+        <v>130330842</v>
       </c>
       <c r="B27" t="n">
-        <v>80316</v>
+        <v>91781</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3487,23 +3491,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444727</v>
+        <v>444550</v>
       </c>
       <c r="R27" t="n">
-        <v>7025514</v>
+        <v>7025500</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande sälg i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3808,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330822</v>
+        <v>130330845</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>83196</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444629</v>
+        <v>444588</v>
       </c>
       <c r="R30" t="n">
-        <v>7025390</v>
+        <v>7025517</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330845</v>
+        <v>130330822</v>
       </c>
       <c r="B31" t="n">
-        <v>83196</v>
+        <v>79211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444588</v>
+        <v>444629</v>
       </c>
       <c r="R31" t="n">
-        <v>7025517</v>
+        <v>7025390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4032,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330838</v>
+        <v>130330859</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>80317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444683</v>
+        <v>444738</v>
       </c>
       <c r="R32" t="n">
-        <v>7025492</v>
+        <v>7025522</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330859</v>
+        <v>130330838</v>
       </c>
       <c r="B33" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444738</v>
+        <v>444683</v>
       </c>
       <c r="R33" t="n">
-        <v>7025522</v>
+        <v>7025492</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330849</v>
+        <v>130330855</v>
       </c>
       <c r="B34" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,30 +4267,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444569</v>
+        <v>444696</v>
       </c>
       <c r="R34" t="n">
-        <v>7025541</v>
+        <v>7025558</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4335,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,12 +4345,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på grov granhögstubbe i gammal granskog nära dike</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,10 +4377,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330855</v>
+        <v>130330850</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>83191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,43 +4388,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444696</v>
+        <v>444566</v>
       </c>
       <c r="R35" t="n">
-        <v>7025558</v>
+        <v>7025535</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4443,7 +4447,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4453,12 +4457,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4485,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330850</v>
+        <v>130330849</v>
       </c>
       <c r="B36" t="n">
-        <v>83191</v>
+        <v>91781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,23 +4500,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444566</v>
+        <v>444569</v>
       </c>
       <c r="R36" t="n">
-        <v>7025535</v>
+        <v>7025541</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på grov granhögstubbe i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330831</v>
+        <v>130330860</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444731</v>
+        <v>444738</v>
       </c>
       <c r="R3" t="n">
-        <v>7025453</v>
+        <v>7025522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330860</v>
+        <v>130330856</v>
       </c>
       <c r="B4" t="n">
-        <v>80316</v>
+        <v>80317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444738</v>
+        <v>444718</v>
       </c>
       <c r="R4" t="n">
-        <v>7025522</v>
+        <v>7025527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330856</v>
+        <v>130330831</v>
       </c>
       <c r="B5" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444718</v>
+        <v>444731</v>
       </c>
       <c r="R5" t="n">
-        <v>7025527</v>
+        <v>7025453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130330857</v>
+        <v>130330824</v>
       </c>
       <c r="B6" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444718</v>
+        <v>444645</v>
       </c>
       <c r="R6" t="n">
-        <v>7025527</v>
+        <v>7025385</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130330824</v>
+        <v>130330857</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444645</v>
+        <v>444718</v>
       </c>
       <c r="R7" t="n">
-        <v>7025385</v>
+        <v>7025527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B10" t="n">
-        <v>91757</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R10" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>91757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R11" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330835</v>
+        <v>130330837</v>
       </c>
       <c r="B14" t="n">
-        <v>80317</v>
+        <v>80316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B15" t="n">
-        <v>80316</v>
+        <v>80317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2243,45 +2243,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130330823</v>
+        <v>130330858</v>
       </c>
       <c r="B16" t="n">
-        <v>97828</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444645</v>
+        <v>444728</v>
       </c>
       <c r="R16" t="n">
-        <v>7025385</v>
+        <v>7025532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,12 +2332,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på marken i gammal granskog</t>
+          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,7 +2364,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130330858</v>
+        <v>130330839</v>
       </c>
       <c r="B17" t="n">
         <v>79211</v>
@@ -2383,26 +2392,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444728</v>
+        <v>444650</v>
       </c>
       <c r="R17" t="n">
-        <v>7025532</v>
+        <v>7025524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
+          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,7 +2476,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130330839</v>
+        <v>130330840</v>
       </c>
       <c r="B18" t="n">
         <v>79211</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444650</v>
+        <v>444637</v>
       </c>
       <c r="R18" t="n">
-        <v>7025524</v>
+        <v>7025502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
+          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130330840</v>
+        <v>130330823</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>97828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444637</v>
+        <v>444645</v>
       </c>
       <c r="R19" t="n">
-        <v>7025502</v>
+        <v>7025385</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3148,34 +3148,30 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130330833</v>
+        <v>130330851</v>
       </c>
       <c r="B24" t="n">
-        <v>80220</v>
+        <v>91781</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3183,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444731</v>
+        <v>444607</v>
       </c>
       <c r="R24" t="n">
-        <v>7025453</v>
+        <v>7025579</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3218,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,12 +3224,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>på död stående gran vid dike/bäck</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130330827</v>
+        <v>130330842</v>
       </c>
       <c r="B25" t="n">
-        <v>80316</v>
+        <v>91781</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,23 +3267,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3295,10 +3287,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444727</v>
+        <v>444550</v>
       </c>
       <c r="R25" t="n">
-        <v>7025514</v>
+        <v>7025500</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3330,7 +3322,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3340,12 +3332,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande sälg i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,30 +3364,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130330851</v>
+        <v>130330833</v>
       </c>
       <c r="B26" t="n">
-        <v>91781</v>
+        <v>80220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3403,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444607</v>
+        <v>444731</v>
       </c>
       <c r="R26" t="n">
-        <v>7025579</v>
+        <v>7025453</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3438,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,12 +3444,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på död stående gran vid dike/bäck</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,10 +3476,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130330842</v>
+        <v>130330827</v>
       </c>
       <c r="B27" t="n">
-        <v>91781</v>
+        <v>80316</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,19 +3487,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444550</v>
+        <v>444727</v>
       </c>
       <c r="R27" t="n">
-        <v>7025500</v>
+        <v>7025514</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>rikligt på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330855</v>
+        <v>130330849</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,43 +4267,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444696</v>
+        <v>444569</v>
       </c>
       <c r="R34" t="n">
-        <v>7025558</v>
+        <v>7025541</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,7 +4322,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4345,12 +4332,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på grov granhögstubbe i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4377,10 +4364,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330850</v>
+        <v>130330855</v>
       </c>
       <c r="B35" t="n">
-        <v>83191</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4388,34 +4375,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444566</v>
+        <v>444696</v>
       </c>
       <c r="R35" t="n">
-        <v>7025535</v>
+        <v>7025558</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4447,7 +4443,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4457,12 +4453,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4489,10 +4485,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330849</v>
+        <v>130330850</v>
       </c>
       <c r="B36" t="n">
-        <v>91781</v>
+        <v>83191</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4500,19 +4496,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444569</v>
+        <v>444566</v>
       </c>
       <c r="R36" t="n">
-        <v>7025541</v>
+        <v>7025535</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på grov granhögstubbe i gammal granskog nära dike</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330860</v>
+        <v>130330856</v>
       </c>
       <c r="B3" t="n">
-        <v>80316</v>
+        <v>80317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444738</v>
+        <v>444718</v>
       </c>
       <c r="R3" t="n">
-        <v>7025522</v>
+        <v>7025527</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330856</v>
+        <v>130330860</v>
       </c>
       <c r="B4" t="n">
-        <v>80317</v>
+        <v>80316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444718</v>
+        <v>444738</v>
       </c>
       <c r="R4" t="n">
-        <v>7025527</v>
+        <v>7025522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>91757</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R10" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B11" t="n">
-        <v>91757</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R11" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2243,54 +2243,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130330858</v>
+        <v>130330823</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>97828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444728</v>
+        <v>444645</v>
       </c>
       <c r="R16" t="n">
-        <v>7025532</v>
+        <v>7025385</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,12 +2323,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
+          <t>på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130330839</v>
+        <v>130330858</v>
       </c>
       <c r="B17" t="n">
         <v>79211</v>
@@ -2392,17 +2383,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444650</v>
+        <v>444728</v>
       </c>
       <c r="R17" t="n">
-        <v>7025524</v>
+        <v>7025532</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
+          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,7 +2476,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130330840</v>
+        <v>130330839</v>
       </c>
       <c r="B18" t="n">
         <v>79211</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444637</v>
+        <v>444650</v>
       </c>
       <c r="R18" t="n">
-        <v>7025502</v>
+        <v>7025524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130330823</v>
+        <v>130330840</v>
       </c>
       <c r="B19" t="n">
-        <v>97828</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444645</v>
+        <v>444637</v>
       </c>
       <c r="R19" t="n">
-        <v>7025385</v>
+        <v>7025502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på marken i gammal granskog</t>
+          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,7 +2700,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130330826</v>
+        <v>130330825</v>
       </c>
       <c r="B20" t="n">
         <v>79211</v>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444727</v>
+        <v>444715</v>
       </c>
       <c r="R20" t="n">
-        <v>7025514</v>
+        <v>7025456</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2812,7 +2812,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130330825</v>
+        <v>130330826</v>
       </c>
       <c r="B21" t="n">
         <v>79211</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444715</v>
+        <v>444727</v>
       </c>
       <c r="R21" t="n">
-        <v>7025456</v>
+        <v>7025514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3148,7 +3148,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130330851</v>
+        <v>130330842</v>
       </c>
       <c r="B24" t="n">
         <v>91781</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444607</v>
+        <v>444550</v>
       </c>
       <c r="R24" t="n">
-        <v>7025579</v>
+        <v>7025500</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på död stående gran vid dike/bäck</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,7 +3256,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130330842</v>
+        <v>130330851</v>
       </c>
       <c r="B25" t="n">
         <v>91781</v>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444550</v>
+        <v>444607</v>
       </c>
       <c r="R25" t="n">
-        <v>7025500</v>
+        <v>7025579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på död stående gran vid dike/bäck</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,32 +3364,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130330833</v>
+        <v>130330827</v>
       </c>
       <c r="B26" t="n">
-        <v>80220</v>
+        <v>80316</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444731</v>
+        <v>444727</v>
       </c>
       <c r="R26" t="n">
-        <v>7025453</v>
+        <v>7025514</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>rikligt på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,32 +3476,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130330827</v>
+        <v>130330833</v>
       </c>
       <c r="B27" t="n">
-        <v>80316</v>
+        <v>80220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444727</v>
+        <v>444731</v>
       </c>
       <c r="R27" t="n">
-        <v>7025514</v>
+        <v>7025453</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande sälg i gammal granskog</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330849</v>
+        <v>130330850</v>
       </c>
       <c r="B34" t="n">
-        <v>91781</v>
+        <v>83191</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,19 +4267,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4287,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444569</v>
+        <v>444566</v>
       </c>
       <c r="R34" t="n">
-        <v>7025541</v>
+        <v>7025535</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,12 +4336,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på grov granhögstubbe i gammal granskog nära dike</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4485,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330850</v>
+        <v>130330849</v>
       </c>
       <c r="B36" t="n">
-        <v>83191</v>
+        <v>91781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,23 +4500,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444566</v>
+        <v>444569</v>
       </c>
       <c r="R36" t="n">
-        <v>7025535</v>
+        <v>7025541</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på grov granhögstubbe i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4597,7 +4597,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130330832</v>
+        <v>130330829</v>
       </c>
       <c r="B37" t="n">
         <v>80316</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>på två gamla sälgar i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330856</v>
+        <v>130330831</v>
       </c>
       <c r="B3" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444718</v>
+        <v>444731</v>
       </c>
       <c r="R3" t="n">
-        <v>7025527</v>
+        <v>7025453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330860</v>
+        <v>130330856</v>
       </c>
       <c r="B4" t="n">
-        <v>80316</v>
+        <v>80317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444738</v>
+        <v>444718</v>
       </c>
       <c r="R4" t="n">
-        <v>7025522</v>
+        <v>7025527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330831</v>
+        <v>130330860</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444731</v>
+        <v>444738</v>
       </c>
       <c r="R5" t="n">
-        <v>7025453</v>
+        <v>7025522</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B10" t="n">
-        <v>91757</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R10" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>91757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R11" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2243,45 +2243,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130330823</v>
+        <v>130330858</v>
       </c>
       <c r="B16" t="n">
-        <v>97828</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444645</v>
+        <v>444728</v>
       </c>
       <c r="R16" t="n">
-        <v>7025385</v>
+        <v>7025532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,12 +2332,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på marken i gammal granskog</t>
+          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,7 +2364,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130330858</v>
+        <v>130330839</v>
       </c>
       <c r="B17" t="n">
         <v>79211</v>
@@ -2383,26 +2392,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444728</v>
+        <v>444650</v>
       </c>
       <c r="R17" t="n">
-        <v>7025532</v>
+        <v>7025524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
+          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,7 +2476,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130330839</v>
+        <v>130330840</v>
       </c>
       <c r="B18" t="n">
         <v>79211</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444650</v>
+        <v>444637</v>
       </c>
       <c r="R18" t="n">
-        <v>7025524</v>
+        <v>7025502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
+          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130330840</v>
+        <v>130330823</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>97828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444637</v>
+        <v>444645</v>
       </c>
       <c r="R19" t="n">
-        <v>7025502</v>
+        <v>7025385</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,7 +2700,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130330825</v>
+        <v>130330826</v>
       </c>
       <c r="B20" t="n">
         <v>79211</v>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444715</v>
+        <v>444727</v>
       </c>
       <c r="R20" t="n">
-        <v>7025456</v>
+        <v>7025514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2812,7 +2812,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130330826</v>
+        <v>130330825</v>
       </c>
       <c r="B21" t="n">
         <v>79211</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444727</v>
+        <v>444715</v>
       </c>
       <c r="R21" t="n">
-        <v>7025514</v>
+        <v>7025456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3808,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330845</v>
+        <v>130330822</v>
       </c>
       <c r="B30" t="n">
-        <v>83196</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444588</v>
+        <v>444629</v>
       </c>
       <c r="R30" t="n">
-        <v>7025517</v>
+        <v>7025390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330822</v>
+        <v>130330845</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>83196</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444629</v>
+        <v>444588</v>
       </c>
       <c r="R31" t="n">
-        <v>7025390</v>
+        <v>7025517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4032,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330859</v>
+        <v>130330838</v>
       </c>
       <c r="B32" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444738</v>
+        <v>444683</v>
       </c>
       <c r="R32" t="n">
-        <v>7025522</v>
+        <v>7025492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330838</v>
+        <v>130330859</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>80317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444683</v>
+        <v>444738</v>
       </c>
       <c r="R33" t="n">
-        <v>7025492</v>
+        <v>7025522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330850</v>
+        <v>130330855</v>
       </c>
       <c r="B34" t="n">
-        <v>83191</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,34 +4267,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444566</v>
+        <v>444696</v>
       </c>
       <c r="R34" t="n">
-        <v>7025535</v>
+        <v>7025558</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4326,7 +4335,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,12 +4345,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4368,10 +4377,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330855</v>
+        <v>130330850</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>83191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,43 +4388,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444696</v>
+        <v>444566</v>
       </c>
       <c r="R35" t="n">
-        <v>7025558</v>
+        <v>7025535</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130330846</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330831</v>
+        <v>130330856</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>80325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444731</v>
+        <v>444718</v>
       </c>
       <c r="R3" t="n">
-        <v>7025453</v>
+        <v>7025527</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330856</v>
+        <v>130330831</v>
       </c>
       <c r="B4" t="n">
-        <v>80317</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444718</v>
+        <v>444731</v>
       </c>
       <c r="R4" t="n">
-        <v>7025527</v>
+        <v>7025453</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>130330860</v>
       </c>
       <c r="B5" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130330824</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130330857</v>
       </c>
       <c r="B7" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130330836</v>
       </c>
       <c r="B8" t="n">
-        <v>80345</v>
+        <v>80353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130330828</v>
       </c>
       <c r="B9" t="n">
-        <v>80352</v>
+        <v>80360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>91770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R10" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B11" t="n">
-        <v>91757</v>
+        <v>79219</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R11" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,7 +1798,7 @@
         <v>130330843</v>
       </c>
       <c r="B12" t="n">
-        <v>75189</v>
+        <v>75197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130330830</v>
       </c>
       <c r="B13" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B14" t="n">
-        <v>80316</v>
+        <v>80325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330835</v>
+        <v>130330837</v>
       </c>
       <c r="B15" t="n">
-        <v>80317</v>
+        <v>80324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
         <v>130330858</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>130330839</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>130330840</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>130330823</v>
       </c>
       <c r="B19" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130330826</v>
+        <v>130330841</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>78231</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,21 +2711,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444727</v>
+        <v>444637</v>
       </c>
       <c r="R20" t="n">
-        <v>7025514</v>
+        <v>7025502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130330825</v>
+        <v>130330826</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444715</v>
+        <v>444727</v>
       </c>
       <c r="R21" t="n">
-        <v>7025456</v>
+        <v>7025514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130330841</v>
+        <v>130330825</v>
       </c>
       <c r="B22" t="n">
-        <v>78223</v>
+        <v>79219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444637</v>
+        <v>444715</v>
       </c>
       <c r="R22" t="n">
-        <v>7025502</v>
+        <v>7025456</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3039,7 +3039,7 @@
         <v>130330854</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>130330842</v>
       </c>
       <c r="B24" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>130330851</v>
       </c>
       <c r="B25" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130330827</v>
+        <v>130330833</v>
       </c>
       <c r="B26" t="n">
-        <v>80316</v>
+        <v>80228</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444727</v>
+        <v>444731</v>
       </c>
       <c r="R26" t="n">
-        <v>7025514</v>
+        <v>7025453</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande sälg i gammal granskog</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,32 +3476,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130330833</v>
+        <v>130330827</v>
       </c>
       <c r="B27" t="n">
-        <v>80220</v>
+        <v>80324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444731</v>
+        <v>444727</v>
       </c>
       <c r="R27" t="n">
-        <v>7025453</v>
+        <v>7025514</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>rikligt på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,7 +3591,7 @@
         <v>130330847</v>
       </c>
       <c r="B28" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>130330848</v>
       </c>
       <c r="B29" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>130330822</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>130330845</v>
       </c>
       <c r="B31" t="n">
-        <v>83196</v>
+        <v>83204</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330838</v>
+        <v>130330859</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>80325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444683</v>
+        <v>444738</v>
       </c>
       <c r="R32" t="n">
-        <v>7025492</v>
+        <v>7025522</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330859</v>
+        <v>130330838</v>
       </c>
       <c r="B33" t="n">
-        <v>80317</v>
+        <v>79219</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444738</v>
+        <v>444683</v>
       </c>
       <c r="R33" t="n">
-        <v>7025522</v>
+        <v>7025492</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330855</v>
+        <v>130330849</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>91794</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,43 +4267,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444696</v>
+        <v>444569</v>
       </c>
       <c r="R34" t="n">
-        <v>7025558</v>
+        <v>7025541</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,7 +4322,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4345,12 +4332,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på grov granhögstubbe i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4377,10 +4364,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330850</v>
+        <v>130330855</v>
       </c>
       <c r="B35" t="n">
-        <v>83191</v>
+        <v>79219</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4388,34 +4375,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444566</v>
+        <v>444696</v>
       </c>
       <c r="R35" t="n">
-        <v>7025535</v>
+        <v>7025558</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4447,7 +4443,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4457,12 +4453,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4489,10 +4485,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330849</v>
+        <v>130330850</v>
       </c>
       <c r="B36" t="n">
-        <v>91781</v>
+        <v>83199</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4500,19 +4496,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444569</v>
+        <v>444566</v>
       </c>
       <c r="R36" t="n">
-        <v>7025541</v>
+        <v>7025535</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på grov granhögstubbe i gammal granskog nära dike</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4597,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130330829</v>
+        <v>130330832</v>
       </c>
       <c r="B37" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på två gamla sälgar i gammal barrblandskog</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4706,6 +4706,3234 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130795562</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57862</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>444696</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7025469</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hördes först födosöka flög sedan till grantopp och hördes sedan locka några meter norrut</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130800368</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>444705</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7025565</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal död gran i gammal granskog, även troliga ringhack</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130800353</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91770</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>444652</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7025557</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande gran (41 cm dbh, ca 175 år ) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130800376</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>444675</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7025530</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130800366</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78231</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>444721</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7025542</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130800374</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83182</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>444662</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7025556</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130795187</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>444732</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7025497</v>
+      </c>
+      <c r="S44" t="n">
+        <v>6</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gammal tall i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130800370</v>
+      </c>
+      <c r="B45" t="n">
+        <v>75197</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>444683</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7025584</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På ved på gren på gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130800372</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>444688</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7025582</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130795383</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80324</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>444726</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7025453</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gammal klen sälg i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130795639</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>444689</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7025495</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt på ca 175 år gammal levande gran (30 cm dbh) i gammal granskog med inslag av glasbjörk och tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130800378</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78231</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>444675</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7025530</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130800355</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>444716</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7025474</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gammal tall med pansarbark, längsta bål 40 cm, i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130800369</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>444704</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7025567</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>80 bålar på gammal levande tall (ca 200 år, 23 cm dbh) i gles gammal barrblandskog, längsta bål 40 cm</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130800359</v>
+      </c>
+      <c r="B52" t="n">
+        <v>75197</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>444731</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7025516</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130800367</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>444721</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7025542</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>200 bålar på gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130800375</v>
+      </c>
+      <c r="B54" t="n">
+        <v>83190</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>492</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>444662</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7025556</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130800358</v>
+      </c>
+      <c r="B55" t="n">
+        <v>85125</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229431</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglavshårprick</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Niesslia lobariae</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Etayo &amp; Diederich</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>444731</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7025516</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På död/döende lunglav 1,8 m upp på grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130800352</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>444700</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7025517</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130800364</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80360</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>444717</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7025526</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130800354</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>444716</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7025439</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130800361</v>
+      </c>
+      <c r="B59" t="n">
+        <v>75309</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Rosa skärelav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Schismatomma pericleum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Branth &amp; Rostr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>444731</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7025516</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130800351</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79219</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>444702</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7025492</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt, minst 50 bålar på gammal levande tall (50 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130800371</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78231</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>444684</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7025581</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130800356</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80325</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>444731</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7025516</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På bark av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130330846</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130330856</v>
       </c>
       <c r="B3" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130330831</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130330860</v>
       </c>
       <c r="B5" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130330824</v>
+        <v>130330857</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>80325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444645</v>
+        <v>444718</v>
       </c>
       <c r="R6" t="n">
-        <v>7025385</v>
+        <v>7025527</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130330857</v>
+        <v>130330824</v>
       </c>
       <c r="B7" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444718</v>
+        <v>444645</v>
       </c>
       <c r="R7" t="n">
-        <v>7025527</v>
+        <v>7025385</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1350,7 @@
         <v>130330836</v>
       </c>
       <c r="B8" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130330828</v>
       </c>
       <c r="B9" t="n">
-        <v>80360</v>
+        <v>80361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>130330852</v>
       </c>
       <c r="B10" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130330834</v>
       </c>
       <c r="B11" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130330843</v>
       </c>
       <c r="B12" t="n">
-        <v>75197</v>
+        <v>75198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130330830</v>
       </c>
       <c r="B13" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330835</v>
+        <v>130330837</v>
       </c>
       <c r="B14" t="n">
         <v>80325</v>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B15" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
         <v>130330858</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>130330839</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>130330840</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>130330823</v>
       </c>
       <c r="B19" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>130330841</v>
       </c>
       <c r="B20" t="n">
-        <v>78231</v>
+        <v>78232</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>130330826</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>130330825</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>130330854</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>130330842</v>
       </c>
       <c r="B24" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>130330851</v>
       </c>
       <c r="B25" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>130330833</v>
       </c>
       <c r="B26" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>130330827</v>
       </c>
       <c r="B27" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>130330847</v>
       </c>
       <c r="B28" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>130330848</v>
       </c>
       <c r="B29" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330822</v>
+        <v>130330845</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>83205</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444629</v>
+        <v>444588</v>
       </c>
       <c r="R30" t="n">
-        <v>7025390</v>
+        <v>7025517</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330845</v>
+        <v>130330822</v>
       </c>
       <c r="B31" t="n">
-        <v>83204</v>
+        <v>79220</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444588</v>
+        <v>444629</v>
       </c>
       <c r="R31" t="n">
-        <v>7025517</v>
+        <v>7025390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4032,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330859</v>
+        <v>130330838</v>
       </c>
       <c r="B32" t="n">
-        <v>80325</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444738</v>
+        <v>444683</v>
       </c>
       <c r="R32" t="n">
-        <v>7025522</v>
+        <v>7025492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330838</v>
+        <v>130330859</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>80326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444683</v>
+        <v>444738</v>
       </c>
       <c r="R33" t="n">
-        <v>7025492</v>
+        <v>7025522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330849</v>
+        <v>130330855</v>
       </c>
       <c r="B34" t="n">
-        <v>91794</v>
+        <v>79220</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,30 +4267,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444569</v>
+        <v>444696</v>
       </c>
       <c r="R34" t="n">
-        <v>7025541</v>
+        <v>7025558</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4335,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,12 +4345,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på grov granhögstubbe i gammal granskog nära dike</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,10 +4377,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330855</v>
+        <v>130330850</v>
       </c>
       <c r="B35" t="n">
-        <v>79219</v>
+        <v>83200</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,43 +4388,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444696</v>
+        <v>444566</v>
       </c>
       <c r="R35" t="n">
-        <v>7025558</v>
+        <v>7025535</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4443,7 +4447,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4453,12 +4457,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4485,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330850</v>
+        <v>130330849</v>
       </c>
       <c r="B36" t="n">
-        <v>83199</v>
+        <v>91795</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,23 +4500,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444566</v>
+        <v>444569</v>
       </c>
       <c r="R36" t="n">
-        <v>7025535</v>
+        <v>7025541</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på grov granhögstubbe i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4600,7 +4600,7 @@
         <v>130330832</v>
       </c>
       <c r="B37" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>130795562</v>
       </c>
       <c r="B38" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>130800368</v>
       </c>
       <c r="B39" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>130800353</v>
       </c>
       <c r="B40" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>130800376</v>
       </c>
       <c r="B41" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>130800366</v>
       </c>
       <c r="B42" t="n">
-        <v>78231</v>
+        <v>78232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>130800374</v>
       </c>
       <c r="B43" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>130795187</v>
       </c>
       <c r="B44" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>130800370</v>
       </c>
       <c r="B45" t="n">
-        <v>75197</v>
+        <v>75198</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>130800372</v>
       </c>
       <c r="B46" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>130795383</v>
       </c>
       <c r="B47" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>130795639</v>
       </c>
       <c r="B48" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>130800378</v>
       </c>
       <c r="B49" t="n">
-        <v>78231</v>
+        <v>78232</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>130800355</v>
       </c>
       <c r="B50" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>130800369</v>
       </c>
       <c r="B51" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>130800359</v>
       </c>
       <c r="B52" t="n">
-        <v>75197</v>
+        <v>75198</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>130800367</v>
       </c>
       <c r="B53" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6781,45 +6781,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130800375</v>
+        <v>130800352</v>
       </c>
       <c r="B54" t="n">
-        <v>83190</v>
+        <v>79220</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444662</v>
+        <v>444700</v>
       </c>
       <c r="R54" t="n">
-        <v>7025556</v>
+        <v>7025517</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6851,7 +6854,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6861,12 +6864,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6875,22 +6878,23 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6908,32 +6912,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800358</v>
+        <v>130800375</v>
       </c>
       <c r="B55" t="n">
-        <v>85125</v>
+        <v>83191</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229431</v>
+        <v>492</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglavshårprick</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Niesslia lobariae</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Etayo &amp; Diederich</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6943,10 +6947,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444731</v>
+        <v>444662</v>
       </c>
       <c r="R55" t="n">
-        <v>7025516</v>
+        <v>7025556</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6978,7 +6982,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6988,36 +6992,36 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På död/döende lunglav 1,8 m upp på grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
         </is>
       </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>lunglav</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7035,48 +7039,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800352</v>
+        <v>130800364</v>
       </c>
       <c r="B56" t="n">
-        <v>79219</v>
+        <v>80361</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444700</v>
+        <v>444717</v>
       </c>
       <c r="R56" t="n">
-        <v>7025517</v>
+        <v>7025526</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7108,7 +7109,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7118,12 +7119,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7132,23 +7133,22 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7166,32 +7166,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800364</v>
+        <v>130800354</v>
       </c>
       <c r="B57" t="n">
-        <v>80360</v>
+        <v>79220</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444717</v>
+        <v>444716</v>
       </c>
       <c r="R57" t="n">
-        <v>7025526</v>
+        <v>7025439</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7265,17 +7265,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7293,10 +7293,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800354</v>
+        <v>130800361</v>
       </c>
       <c r="B58" t="n">
-        <v>79219</v>
+        <v>75310</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7304,21 +7304,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7328,10 +7328,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444716</v>
+        <v>444731</v>
       </c>
       <c r="R58" t="n">
-        <v>7025439</v>
+        <v>7025516</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,17 +7392,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800361</v>
+        <v>130800351</v>
       </c>
       <c r="B59" t="n">
-        <v>75309</v>
+        <v>79220</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7431,34 +7431,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444731</v>
+        <v>444702</v>
       </c>
       <c r="R59" t="n">
-        <v>7025516</v>
+        <v>7025492</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7490,7 +7499,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7500,12 +7509,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>Rikligt, minst 50 bålar på gammal levande tall (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7519,17 +7528,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7547,10 +7556,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800351</v>
+        <v>130800356</v>
       </c>
       <c r="B60" t="n">
-        <v>79219</v>
+        <v>80326</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7558,43 +7567,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444702</v>
+        <v>444731</v>
       </c>
       <c r="R60" t="n">
-        <v>7025492</v>
+        <v>7025516</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt, minst 50 bålar på gammal levande tall (50 cm dbh) i gammal granskog</t>
+          <t>På bark av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7655,17 +7655,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7686,7 +7686,7 @@
         <v>130800371</v>
       </c>
       <c r="B61" t="n">
-        <v>78231</v>
+        <v>78232</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,10 +7810,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130800356</v>
+        <v>130812174</v>
       </c>
       <c r="B62" t="n">
-        <v>80325</v>
+        <v>83195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7821,21 +7821,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7845,10 +7845,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444731</v>
+        <v>444717</v>
       </c>
       <c r="R62" t="n">
-        <v>7025516</v>
+        <v>7025526</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7890,12 +7890,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>på bark på stam av gammal lutande, levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7934,6 +7934,141 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130800358</v>
+      </c>
+      <c r="B63" t="n">
+        <v>85126</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229431</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lunglavshårprick</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Niesslia lobariae</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Etayo &amp; Diederich</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>444731</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7025516</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På död/döende lunglav 1,8 m upp på grov gammal levande sälg (50 cm dbh) i gammal granskog. Mikroskoperad, seta bruna, 75 my långa, 6 my närmare basen gradvis avsmalnande, torra perithecier kollapsade enligt bild i Etayo &amp; Diederich 1996.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130330846</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330856</v>
+        <v>130330831</v>
       </c>
       <c r="B3" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444718</v>
+        <v>444731</v>
       </c>
       <c r="R3" t="n">
-        <v>7025527</v>
+        <v>7025453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330831</v>
+        <v>130330860</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444731</v>
+        <v>444738</v>
       </c>
       <c r="R4" t="n">
-        <v>7025453</v>
+        <v>7025522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330860</v>
+        <v>130330856</v>
       </c>
       <c r="B5" t="n">
-        <v>80325</v>
+        <v>80327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444738</v>
+        <v>444718</v>
       </c>
       <c r="R5" t="n">
-        <v>7025522</v>
+        <v>7025527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130330857</v>
+        <v>130330824</v>
       </c>
       <c r="B6" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444718</v>
+        <v>444645</v>
       </c>
       <c r="R6" t="n">
-        <v>7025527</v>
+        <v>7025385</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130330824</v>
+        <v>130330857</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444645</v>
+        <v>444718</v>
       </c>
       <c r="R7" t="n">
-        <v>7025385</v>
+        <v>7025527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1350,7 @@
         <v>130330836</v>
       </c>
       <c r="B8" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130330828</v>
       </c>
       <c r="B9" t="n">
-        <v>80361</v>
+        <v>80362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>130330852</v>
       </c>
       <c r="B10" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130330834</v>
       </c>
       <c r="B11" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130330843</v>
       </c>
       <c r="B12" t="n">
-        <v>75198</v>
+        <v>75199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130330830</v>
       </c>
       <c r="B13" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>130330837</v>
       </c>
       <c r="B14" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>130330835</v>
       </c>
       <c r="B15" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>130330858</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>130330839</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>130330840</v>
       </c>
       <c r="B18" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>130330823</v>
       </c>
       <c r="B19" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>130330841</v>
       </c>
       <c r="B20" t="n">
-        <v>78232</v>
+        <v>78233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>130330826</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>130330825</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>130330854</v>
       </c>
       <c r="B23" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>130330842</v>
       </c>
       <c r="B24" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>130330851</v>
       </c>
       <c r="B25" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>130330833</v>
       </c>
       <c r="B26" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>130330827</v>
       </c>
       <c r="B27" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>130330847</v>
       </c>
       <c r="B28" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>130330848</v>
       </c>
       <c r="B29" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330845</v>
+        <v>130330822</v>
       </c>
       <c r="B30" t="n">
-        <v>83205</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444588</v>
+        <v>444629</v>
       </c>
       <c r="R30" t="n">
-        <v>7025517</v>
+        <v>7025390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330822</v>
+        <v>130330845</v>
       </c>
       <c r="B31" t="n">
-        <v>79220</v>
+        <v>83206</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444629</v>
+        <v>444588</v>
       </c>
       <c r="R31" t="n">
-        <v>7025390</v>
+        <v>7025517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4032,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330838</v>
+        <v>130330859</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>80327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444683</v>
+        <v>444738</v>
       </c>
       <c r="R32" t="n">
-        <v>7025492</v>
+        <v>7025522</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330859</v>
+        <v>130330838</v>
       </c>
       <c r="B33" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444738</v>
+        <v>444683</v>
       </c>
       <c r="R33" t="n">
-        <v>7025522</v>
+        <v>7025492</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330855</v>
+        <v>130330849</v>
       </c>
       <c r="B34" t="n">
-        <v>79220</v>
+        <v>91796</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,43 +4267,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444696</v>
+        <v>444569</v>
       </c>
       <c r="R34" t="n">
-        <v>7025558</v>
+        <v>7025541</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,7 +4322,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4345,12 +4332,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>på grov granhögstubbe i gammal granskog nära dike</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4377,10 +4364,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330850</v>
+        <v>130330855</v>
       </c>
       <c r="B35" t="n">
-        <v>83200</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4388,34 +4375,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444566</v>
+        <v>444696</v>
       </c>
       <c r="R35" t="n">
-        <v>7025535</v>
+        <v>7025558</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4447,7 +4443,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4457,12 +4453,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4489,10 +4485,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330849</v>
+        <v>130330850</v>
       </c>
       <c r="B36" t="n">
-        <v>91795</v>
+        <v>83201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4500,19 +4496,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444569</v>
+        <v>444566</v>
       </c>
       <c r="R36" t="n">
-        <v>7025541</v>
+        <v>7025535</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på grov granhögstubbe i gammal granskog nära dike</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4600,7 +4600,7 @@
         <v>130330832</v>
       </c>
       <c r="B37" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>130795562</v>
       </c>
       <c r="B38" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>130800368</v>
       </c>
       <c r="B39" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>130800353</v>
       </c>
       <c r="B40" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>130800376</v>
       </c>
       <c r="B41" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>130800366</v>
       </c>
       <c r="B42" t="n">
-        <v>78232</v>
+        <v>78233</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>130800374</v>
       </c>
       <c r="B43" t="n">
-        <v>83183</v>
+        <v>83184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>130795187</v>
       </c>
       <c r="B44" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>130800370</v>
       </c>
       <c r="B45" t="n">
-        <v>75198</v>
+        <v>75199</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5738,10 +5738,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800372</v>
+        <v>130795383</v>
       </c>
       <c r="B46" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5749,34 +5749,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444688</v>
+        <v>444726</v>
       </c>
       <c r="R46" t="n">
-        <v>7025582</v>
+        <v>7025453</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal klen sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5837,17 +5837,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130795383</v>
+        <v>130800372</v>
       </c>
       <c r="B47" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5876,34 +5876,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444726</v>
+        <v>444688</v>
       </c>
       <c r="R47" t="n">
-        <v>7025453</v>
+        <v>7025582</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal klen sälg i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5964,17 +5964,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
         <v>130795639</v>
       </c>
       <c r="B48" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>130800378</v>
       </c>
       <c r="B49" t="n">
-        <v>78232</v>
+        <v>78233</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6255,32 +6255,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800355</v>
+        <v>130800359</v>
       </c>
       <c r="B50" t="n">
-        <v>79220</v>
+        <v>75199</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444716</v>
+        <v>444731</v>
       </c>
       <c r="R50" t="n">
-        <v>7025474</v>
+        <v>7025516</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal tall med pansarbark, längsta bål 40 cm, i gammal granskog</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6354,17 +6354,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6382,10 +6382,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130800369</v>
+        <v>130800355</v>
       </c>
       <c r="B51" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6410,26 +6410,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444704</v>
+        <v>444716</v>
       </c>
       <c r="R51" t="n">
-        <v>7025567</v>
+        <v>7025474</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6461,7 +6452,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6471,12 +6462,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>80 bålar på gammal levande tall (ca 200 år, 23 cm dbh) i gles gammal barrblandskog, längsta bål 40 cm</t>
+          <t>På gammal tall med pansarbark, längsta bål 40 cm, i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6518,45 +6509,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130800359</v>
+        <v>130800369</v>
       </c>
       <c r="B52" t="n">
-        <v>75198</v>
+        <v>79221</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444731</v>
+        <v>444704</v>
       </c>
       <c r="R52" t="n">
-        <v>7025516</v>
+        <v>7025567</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>80 bålar på gammal levande tall (ca 200 år, 23 cm dbh) i gles gammal barrblandskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6617,17 +6617,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
         <v>130800367</v>
       </c>
       <c r="B53" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6781,48 +6781,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130800352</v>
+        <v>130800375</v>
       </c>
       <c r="B54" t="n">
-        <v>79220</v>
+        <v>83192</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444700</v>
+        <v>444662</v>
       </c>
       <c r="R54" t="n">
-        <v>7025517</v>
+        <v>7025556</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6854,7 +6851,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6864,12 +6861,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6878,23 +6875,22 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6912,45 +6908,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800375</v>
+        <v>130800352</v>
       </c>
       <c r="B55" t="n">
-        <v>83191</v>
+        <v>79221</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444662</v>
+        <v>444700</v>
       </c>
       <c r="R55" t="n">
-        <v>7025556</v>
+        <v>7025517</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6982,7 +6981,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6992,12 +6991,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7006,22 +7005,23 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7042,7 +7042,7 @@
         <v>130800364</v>
       </c>
       <c r="B56" t="n">
-        <v>80361</v>
+        <v>80362</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800354</v>
+        <v>130800361</v>
       </c>
       <c r="B57" t="n">
-        <v>79220</v>
+        <v>75311</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7177,21 +7177,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444716</v>
+        <v>444731</v>
       </c>
       <c r="R57" t="n">
-        <v>7025439</v>
+        <v>7025516</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7265,17 +7265,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7293,10 +7293,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800361</v>
+        <v>130800354</v>
       </c>
       <c r="B58" t="n">
-        <v>75310</v>
+        <v>79221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7304,21 +7304,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7328,10 +7328,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444731</v>
+        <v>444716</v>
       </c>
       <c r="R58" t="n">
-        <v>7025516</v>
+        <v>7025439</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,17 +7392,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7423,7 +7423,7 @@
         <v>130800351</v>
       </c>
       <c r="B59" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>130800356</v>
       </c>
       <c r="B60" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>130800371</v>
       </c>
       <c r="B61" t="n">
-        <v>78232</v>
+        <v>78233</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>130812174</v>
       </c>
       <c r="B62" t="n">
-        <v>83195</v>
+        <v>83196</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>130800358</v>
       </c>
       <c r="B63" t="n">
-        <v>85126</v>
+        <v>85127</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330831</v>
+        <v>130330856</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>80327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444731</v>
+        <v>444718</v>
       </c>
       <c r="R3" t="n">
-        <v>7025453</v>
+        <v>7025527</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330860</v>
+        <v>130330831</v>
       </c>
       <c r="B4" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444738</v>
+        <v>444731</v>
       </c>
       <c r="R4" t="n">
-        <v>7025522</v>
+        <v>7025453</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330856</v>
+        <v>130330860</v>
       </c>
       <c r="B5" t="n">
-        <v>80327</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444718</v>
+        <v>444738</v>
       </c>
       <c r="R5" t="n">
-        <v>7025527</v>
+        <v>7025522</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130330824</v>
+        <v>130330857</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444645</v>
+        <v>444718</v>
       </c>
       <c r="R6" t="n">
-        <v>7025385</v>
+        <v>7025527</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130330857</v>
+        <v>130330824</v>
       </c>
       <c r="B7" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444718</v>
+        <v>444645</v>
       </c>
       <c r="R7" t="n">
-        <v>7025527</v>
+        <v>7025385</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330835</v>
+        <v>130330837</v>
       </c>
       <c r="B15" t="n">
-        <v>80327</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330822</v>
+        <v>130330845</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>83206</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444629</v>
+        <v>444588</v>
       </c>
       <c r="R30" t="n">
-        <v>7025390</v>
+        <v>7025517</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330845</v>
+        <v>130330822</v>
       </c>
       <c r="B31" t="n">
-        <v>83206</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444588</v>
+        <v>444629</v>
       </c>
       <c r="R31" t="n">
-        <v>7025517</v>
+        <v>7025390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5348,48 +5348,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800374</v>
+        <v>130795187</v>
       </c>
       <c r="B43" t="n">
-        <v>83184</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444662</v>
+        <v>444732</v>
       </c>
       <c r="R43" t="n">
-        <v>7025556</v>
+        <v>7025497</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5418,7 +5427,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5428,12 +5437,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+          <t>På gammal tall i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5447,17 +5456,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5475,57 +5484,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130795187</v>
+        <v>130800374</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>83184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444732</v>
+        <v>444662</v>
       </c>
       <c r="R44" t="n">
-        <v>7025497</v>
+        <v>7025556</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal tall i gammal granskog</t>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5583,17 +5583,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5738,10 +5738,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130795383</v>
+        <v>130800372</v>
       </c>
       <c r="B46" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5749,34 +5749,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444726</v>
+        <v>444688</v>
       </c>
       <c r="R46" t="n">
-        <v>7025453</v>
+        <v>7025582</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal klen sälg i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5837,17 +5837,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130800372</v>
+        <v>130795383</v>
       </c>
       <c r="B47" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5876,34 +5876,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444688</v>
+        <v>444726</v>
       </c>
       <c r="R47" t="n">
-        <v>7025582</v>
+        <v>7025453</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal klen sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5964,17 +5964,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6255,32 +6255,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800359</v>
+        <v>130800355</v>
       </c>
       <c r="B50" t="n">
-        <v>75199</v>
+        <v>79221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444731</v>
+        <v>444716</v>
       </c>
       <c r="R50" t="n">
-        <v>7025516</v>
+        <v>7025474</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>På gammal tall med pansarbark, längsta bål 40 cm, i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6354,17 +6354,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6382,7 +6382,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130800355</v>
+        <v>130800369</v>
       </c>
       <c r="B51" t="n">
         <v>79221</v>
@@ -6410,17 +6410,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444716</v>
+        <v>444704</v>
       </c>
       <c r="R51" t="n">
-        <v>7025474</v>
+        <v>7025567</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6452,7 +6461,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6462,12 +6471,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal tall med pansarbark, längsta bål 40 cm, i gammal granskog</t>
+          <t>80 bålar på gammal levande tall (ca 200 år, 23 cm dbh) i gles gammal barrblandskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6509,54 +6518,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130800369</v>
+        <v>130800359</v>
       </c>
       <c r="B52" t="n">
-        <v>79221</v>
+        <v>75199</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444704</v>
+        <v>444731</v>
       </c>
       <c r="R52" t="n">
-        <v>7025567</v>
+        <v>7025516</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>80 bålar på gammal levande tall (ca 200 år, 23 cm dbh) i gles gammal barrblandskog, längsta bål 40 cm</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6617,17 +6617,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7039,32 +7039,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800364</v>
+        <v>130800361</v>
       </c>
       <c r="B56" t="n">
-        <v>80362</v>
+        <v>75311</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>1460</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444717</v>
+        <v>444731</v>
       </c>
       <c r="R56" t="n">
-        <v>7025526</v>
+        <v>7025516</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7166,32 +7166,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800361</v>
+        <v>130800364</v>
       </c>
       <c r="B57" t="n">
-        <v>75311</v>
+        <v>80362</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1460</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444731</v>
+        <v>444717</v>
       </c>
       <c r="R57" t="n">
-        <v>7025516</v>
+        <v>7025526</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330852</v>
+        <v>130330834</v>
       </c>
       <c r="B10" t="n">
-        <v>91772</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444675</v>
+        <v>444722</v>
       </c>
       <c r="R10" t="n">
-        <v>7025575</v>
+        <v>7025477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330834</v>
+        <v>130330852</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>91772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444722</v>
+        <v>444675</v>
       </c>
       <c r="R11" t="n">
-        <v>7025477</v>
+        <v>7025575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330835</v>
+        <v>130330837</v>
       </c>
       <c r="B14" t="n">
-        <v>80327</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B15" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130330841</v>
+        <v>130330826</v>
       </c>
       <c r="B20" t="n">
-        <v>78233</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,21 +2711,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444637</v>
+        <v>444727</v>
       </c>
       <c r="R20" t="n">
-        <v>7025502</v>
+        <v>7025514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,7 +2812,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130330826</v>
+        <v>130330825</v>
       </c>
       <c r="B21" t="n">
         <v>79221</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444727</v>
+        <v>444715</v>
       </c>
       <c r="R21" t="n">
-        <v>7025514</v>
+        <v>7025456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130330825</v>
+        <v>130330841</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>78233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444715</v>
+        <v>444637</v>
       </c>
       <c r="R22" t="n">
-        <v>7025456</v>
+        <v>7025502</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3808,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330845</v>
+        <v>130330822</v>
       </c>
       <c r="B30" t="n">
-        <v>83206</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444588</v>
+        <v>444629</v>
       </c>
       <c r="R30" t="n">
-        <v>7025517</v>
+        <v>7025390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330822</v>
+        <v>130330845</v>
       </c>
       <c r="B31" t="n">
-        <v>79221</v>
+        <v>83206</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444629</v>
+        <v>444588</v>
       </c>
       <c r="R31" t="n">
-        <v>7025390</v>
+        <v>7025517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4032,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330859</v>
+        <v>130330838</v>
       </c>
       <c r="B32" t="n">
-        <v>80327</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444738</v>
+        <v>444683</v>
       </c>
       <c r="R32" t="n">
-        <v>7025522</v>
+        <v>7025492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330838</v>
+        <v>130330859</v>
       </c>
       <c r="B33" t="n">
-        <v>79221</v>
+        <v>80327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444683</v>
+        <v>444738</v>
       </c>
       <c r="R33" t="n">
-        <v>7025492</v>
+        <v>7025522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5348,57 +5348,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130795187</v>
+        <v>130800374</v>
       </c>
       <c r="B43" t="n">
-        <v>79221</v>
+        <v>83184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444732</v>
+        <v>444662</v>
       </c>
       <c r="R43" t="n">
-        <v>7025497</v>
+        <v>7025556</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5427,7 +5418,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5437,12 +5428,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal tall i gammal granskog</t>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5456,17 +5447,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5484,48 +5475,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800374</v>
+        <v>130795187</v>
       </c>
       <c r="B44" t="n">
-        <v>83184</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444662</v>
+        <v>444732</v>
       </c>
       <c r="R44" t="n">
-        <v>7025556</v>
+        <v>7025497</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+          <t>På gammal tall i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5583,17 +5583,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5738,10 +5738,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800372</v>
+        <v>130795383</v>
       </c>
       <c r="B46" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5749,34 +5749,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444688</v>
+        <v>444726</v>
       </c>
       <c r="R46" t="n">
-        <v>7025582</v>
+        <v>7025453</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal klen sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5837,17 +5837,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130795383</v>
+        <v>130800372</v>
       </c>
       <c r="B47" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5876,34 +5876,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444726</v>
+        <v>444688</v>
       </c>
       <c r="R47" t="n">
-        <v>7025453</v>
+        <v>7025582</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal klen sälg i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5964,17 +5964,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6781,45 +6781,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130800375</v>
+        <v>130800352</v>
       </c>
       <c r="B54" t="n">
-        <v>83192</v>
+        <v>79221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444662</v>
+        <v>444700</v>
       </c>
       <c r="R54" t="n">
-        <v>7025556</v>
+        <v>7025517</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6851,7 +6854,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6861,12 +6864,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6875,22 +6878,23 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6908,48 +6912,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800352</v>
+        <v>130800375</v>
       </c>
       <c r="B55" t="n">
-        <v>79221</v>
+        <v>83192</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444700</v>
+        <v>444662</v>
       </c>
       <c r="R55" t="n">
-        <v>7025517</v>
+        <v>7025556</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6981,7 +6982,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6991,12 +6992,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7005,23 +7006,22 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7039,10 +7039,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800361</v>
+        <v>130800354</v>
       </c>
       <c r="B56" t="n">
-        <v>75311</v>
+        <v>79221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7050,21 +7050,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444731</v>
+        <v>444716</v>
       </c>
       <c r="R56" t="n">
-        <v>7025516</v>
+        <v>7025439</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,17 +7138,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7166,32 +7166,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800364</v>
+        <v>130800361</v>
       </c>
       <c r="B57" t="n">
-        <v>80362</v>
+        <v>75311</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>1460</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444717</v>
+        <v>444731</v>
       </c>
       <c r="R57" t="n">
-        <v>7025526</v>
+        <v>7025516</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7293,32 +7293,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800354</v>
+        <v>130800364</v>
       </c>
       <c r="B58" t="n">
-        <v>79221</v>
+        <v>80362</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7328,10 +7328,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444716</v>
+        <v>444717</v>
       </c>
       <c r="R58" t="n">
-        <v>7025439</v>
+        <v>7025526</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,17 +7392,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7556,10 +7556,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800356</v>
+        <v>130800371</v>
       </c>
       <c r="B60" t="n">
-        <v>80327</v>
+        <v>78233</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7567,21 +7567,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444731</v>
+        <v>444684</v>
       </c>
       <c r="R60" t="n">
-        <v>7025516</v>
+        <v>7025581</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På bark av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7655,17 +7655,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800371</v>
+        <v>130800356</v>
       </c>
       <c r="B61" t="n">
-        <v>78233</v>
+        <v>80327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7694,21 +7694,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444684</v>
+        <v>444731</v>
       </c>
       <c r="R61" t="n">
-        <v>7025581</v>
+        <v>7025516</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7782,17 +7782,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -5348,48 +5348,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800374</v>
+        <v>130795187</v>
       </c>
       <c r="B43" t="n">
-        <v>83184</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444662</v>
+        <v>444732</v>
       </c>
       <c r="R43" t="n">
-        <v>7025556</v>
+        <v>7025497</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5418,7 +5427,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5428,12 +5437,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+          <t>På gammal tall i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5447,17 +5456,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5475,57 +5484,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130795187</v>
+        <v>130800374</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>83184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444732</v>
+        <v>444662</v>
       </c>
       <c r="R44" t="n">
-        <v>7025497</v>
+        <v>7025556</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal tall i gammal granskog</t>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5583,17 +5583,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5738,10 +5738,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130795383</v>
+        <v>130800372</v>
       </c>
       <c r="B46" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5749,34 +5749,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444726</v>
+        <v>444688</v>
       </c>
       <c r="R46" t="n">
-        <v>7025453</v>
+        <v>7025582</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal klen sälg i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5837,17 +5837,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130800372</v>
+        <v>130795383</v>
       </c>
       <c r="B47" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5876,34 +5876,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444688</v>
+        <v>444726</v>
       </c>
       <c r="R47" t="n">
-        <v>7025582</v>
+        <v>7025453</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal klen sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5964,17 +5964,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7039,10 +7039,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800354</v>
+        <v>130800361</v>
       </c>
       <c r="B56" t="n">
-        <v>79221</v>
+        <v>75311</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7050,21 +7050,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444716</v>
+        <v>444731</v>
       </c>
       <c r="R56" t="n">
-        <v>7025439</v>
+        <v>7025516</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,17 +7138,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7166,32 +7166,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800361</v>
+        <v>130800364</v>
       </c>
       <c r="B57" t="n">
-        <v>75311</v>
+        <v>80362</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1460</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444731</v>
+        <v>444717</v>
       </c>
       <c r="R57" t="n">
-        <v>7025516</v>
+        <v>7025526</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7293,32 +7293,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800364</v>
+        <v>130800354</v>
       </c>
       <c r="B58" t="n">
-        <v>80362</v>
+        <v>79221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7328,10 +7328,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444717</v>
+        <v>444716</v>
       </c>
       <c r="R58" t="n">
-        <v>7025526</v>
+        <v>7025439</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,17 +7392,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7556,10 +7556,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800371</v>
+        <v>130800356</v>
       </c>
       <c r="B60" t="n">
-        <v>78233</v>
+        <v>80327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7567,21 +7567,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444684</v>
+        <v>444731</v>
       </c>
       <c r="R60" t="n">
-        <v>7025581</v>
+        <v>7025516</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7655,17 +7655,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800356</v>
+        <v>130800371</v>
       </c>
       <c r="B61" t="n">
-        <v>80327</v>
+        <v>78233</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7694,21 +7694,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444731</v>
+        <v>444684</v>
       </c>
       <c r="R61" t="n">
-        <v>7025516</v>
+        <v>7025581</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På bark av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7782,17 +7782,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8070,6 +8070,1713 @@
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>133825706</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>444728</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7025454</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>115 skott på marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>133825703</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79712</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>257107</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blek lundlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Bacidia rosellizans</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>S.Ekman</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>444737</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7025451</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gammal asp i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>133825700</v>
+      </c>
+      <c r="B66" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>444713</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7025498</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>133825702</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>444726</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7025477</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>97 plantor inom 2x2 m i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>133825713</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92641</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>444671</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7025477</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På grov granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>133825708</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>444731</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7025449</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På klen gammal granlåga</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>133825711</v>
+      </c>
+      <c r="B70" t="n">
+        <v>83306</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>492</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>444718</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7025467</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>133825701</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>444721</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7025487</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>133825707</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>444725</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7025460</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>8 skott inom 1x1 m i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>133825718</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92878</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>444672</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7025569</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>I gammal fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>133825717</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101338</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>444683</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7025604</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På marken längs bäck</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>133825710</v>
+      </c>
+      <c r="B75" t="n">
+        <v>83298</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>444718</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7025467</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>133825712</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>444721</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7025472</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog med tallöverståndare</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>133825705</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>444725</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7025449</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>32 skott inom 0,7x0,5 m på marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8075,7 +8075,7 @@
         <v>133825706</v>
       </c>
       <c r="B64" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8186,55 +8186,52 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133825703</v>
+        <v>133825700</v>
       </c>
       <c r="B65" t="n">
-        <v>79712</v>
+        <v>96350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>257107</v>
+        <v>2809</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444737</v>
+        <v>444713</v>
       </c>
       <c r="R65" t="n">
-        <v>7025451</v>
+        <v>7025498</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8266,7 +8263,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8276,12 +8273,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8290,24 +8287,8 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8317,52 +8298,55 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133825700</v>
+        <v>133825703</v>
       </c>
       <c r="B66" t="n">
-        <v>96348</v>
+        <v>79713</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>257107</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444713</v>
+        <v>444737</v>
       </c>
       <c r="R66" t="n">
-        <v>7025498</v>
+        <v>7025451</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8394,7 +8378,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8404,12 +8388,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8418,8 +8402,24 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8439,7 +8439,7 @@
         <v>133825702</v>
       </c>
       <c r="B67" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8550,39 +8550,39 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825713</v>
+        <v>133825711</v>
       </c>
       <c r="B68" t="n">
-        <v>92641</v>
+        <v>83307</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444671</v>
+        <v>444718</v>
       </c>
       <c r="R68" t="n">
-        <v>7025477</v>
+        <v>7025467</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8656,17 +8656,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8687,7 +8687,7 @@
         <v>133825708</v>
       </c>
       <c r="B69" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8811,32 +8811,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825711</v>
+        <v>133825713</v>
       </c>
       <c r="B70" t="n">
-        <v>83306</v>
+        <v>92643</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>492</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444718</v>
+        <v>444671</v>
       </c>
       <c r="R70" t="n">
-        <v>7025467</v>
+        <v>7025477</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8910,17 +8910,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8941,7 +8941,7 @@
         <v>133825701</v>
       </c>
       <c r="B71" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
         <v>133825707</v>
       </c>
       <c r="B72" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>133825718</v>
       </c>
       <c r="B73" t="n">
-        <v>92878</v>
+        <v>92880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9295,7 +9295,7 @@
         <v>133825717</v>
       </c>
       <c r="B74" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9407,7 +9407,7 @@
         <v>133825710</v>
       </c>
       <c r="B75" t="n">
-        <v>83298</v>
+        <v>83299</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9534,7 +9534,7 @@
         <v>133825712</v>
       </c>
       <c r="B76" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>133825705</v>
       </c>
       <c r="B77" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8075,7 +8075,7 @@
         <v>133825706</v>
       </c>
       <c r="B64" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8196,7 +8196,7 @@
         <v>133825700</v>
       </c>
       <c r="B65" t="n">
-        <v>96350</v>
+        <v>96356</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8439,7 +8439,7 @@
         <v>133825702</v>
       </c>
       <c r="B67" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8550,17 +8550,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825711</v>
+        <v>133825701</v>
       </c>
       <c r="B68" t="n">
-        <v>83307</v>
+        <v>99138</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8568,34 +8568,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444718</v>
+        <v>444721</v>
       </c>
       <c r="R68" t="n">
-        <v>7025467</v>
+        <v>7025487</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8627,7 +8636,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8637,12 +8646,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8653,21 +8662,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8677,52 +8671,61 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825708</v>
+        <v>133825707</v>
       </c>
       <c r="B69" t="n">
-        <v>91920</v>
+        <v>99138</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444731</v>
+        <v>444725</v>
       </c>
       <c r="R69" t="n">
-        <v>7025449</v>
+        <v>7025460</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8754,7 +8757,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8764,12 +8767,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>8 skott inom 1x1 m i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8780,21 +8783,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8811,32 +8799,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825713</v>
+        <v>133825711</v>
       </c>
       <c r="B70" t="n">
-        <v>92643</v>
+        <v>83309</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>492</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8846,10 +8834,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444671</v>
+        <v>444718</v>
       </c>
       <c r="R70" t="n">
-        <v>7025477</v>
+        <v>7025467</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8881,7 +8869,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8891,12 +8879,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8910,17 +8898,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8931,61 +8919,52 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133825701</v>
+        <v>133825708</v>
       </c>
       <c r="B71" t="n">
-        <v>99132</v>
+        <v>91926</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444721</v>
+        <v>444731</v>
       </c>
       <c r="R71" t="n">
-        <v>7025487</v>
+        <v>7025449</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9017,7 +8996,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9027,12 +9006,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9043,6 +9022,21 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9052,61 +9046,52 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133825707</v>
+        <v>133825713</v>
       </c>
       <c r="B72" t="n">
-        <v>99132</v>
+        <v>92649</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444725</v>
+        <v>444671</v>
       </c>
       <c r="R72" t="n">
-        <v>7025460</v>
+        <v>7025477</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9138,7 +9123,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9148,12 +9133,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>8 skott inom 1x1 m i gammal granskog</t>
+          <t>På grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9164,6 +9149,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9183,7 +9183,7 @@
         <v>133825718</v>
       </c>
       <c r="B73" t="n">
-        <v>92880</v>
+        <v>92886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9295,7 +9295,7 @@
         <v>133825717</v>
       </c>
       <c r="B74" t="n">
-        <v>101340</v>
+        <v>101346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9407,7 +9407,7 @@
         <v>133825710</v>
       </c>
       <c r="B75" t="n">
-        <v>83299</v>
+        <v>83301</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9534,7 +9534,7 @@
         <v>133825712</v>
       </c>
       <c r="B76" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>133825705</v>
       </c>
       <c r="B77" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8075,7 +8075,7 @@
         <v>133825706</v>
       </c>
       <c r="B64" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>133825700</v>
       </c>
       <c r="B65" t="n">
-        <v>96356</v>
+        <v>96358</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>133825702</v>
       </c>
       <c r="B67" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8557,54 +8557,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825701</v>
+        <v>133825713</v>
       </c>
       <c r="B68" t="n">
-        <v>99138</v>
+        <v>92651</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444721</v>
+        <v>444671</v>
       </c>
       <c r="R68" t="n">
-        <v>7025487</v>
+        <v>7025477</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8636,7 +8627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8646,12 +8637,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>På grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8662,6 +8653,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8678,10 +8684,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825707</v>
+        <v>133825711</v>
       </c>
       <c r="B69" t="n">
-        <v>99138</v>
+        <v>83310</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8689,43 +8695,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>492</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444725</v>
+        <v>444718</v>
       </c>
       <c r="R69" t="n">
-        <v>7025460</v>
+        <v>7025467</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8757,7 +8754,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8767,12 +8764,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>8 skott inom 1x1 m i gammal granskog</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8783,6 +8780,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8799,32 +8811,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825711</v>
+        <v>133825708</v>
       </c>
       <c r="B70" t="n">
-        <v>83309</v>
+        <v>91928</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8834,10 +8846,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444718</v>
+        <v>444731</v>
       </c>
       <c r="R70" t="n">
-        <v>7025467</v>
+        <v>7025449</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8869,7 +8881,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8879,12 +8891,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8898,17 +8910,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8926,45 +8938,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133825708</v>
+        <v>133825701</v>
       </c>
       <c r="B71" t="n">
-        <v>91926</v>
+        <v>99140</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444731</v>
+        <v>444721</v>
       </c>
       <c r="R71" t="n">
-        <v>7025449</v>
+        <v>7025487</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8996,7 +9017,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9006,12 +9027,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9022,21 +9043,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9053,45 +9059,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133825713</v>
+        <v>133825707</v>
       </c>
       <c r="B72" t="n">
-        <v>92649</v>
+        <v>99140</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444671</v>
+        <v>444725</v>
       </c>
       <c r="R72" t="n">
-        <v>7025477</v>
+        <v>7025460</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9123,7 +9138,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9133,12 +9148,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe</t>
+          <t>8 skott inom 1x1 m i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9149,21 +9164,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9183,7 +9183,7 @@
         <v>133825718</v>
       </c>
       <c r="B73" t="n">
-        <v>92886</v>
+        <v>92888</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>133825717</v>
       </c>
       <c r="B74" t="n">
-        <v>101346</v>
+        <v>101348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>133825710</v>
       </c>
       <c r="B75" t="n">
-        <v>83301</v>
+        <v>83302</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>133825712</v>
       </c>
       <c r="B76" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>133825705</v>
       </c>
       <c r="B77" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9777,6 +9777,133 @@
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>130800360</v>
+      </c>
+      <c r="B78" t="n">
+        <v>75426</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1776</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Amerikansk sönderfallslav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Bactrospora brodoi</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Litnersmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>444731</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7025516</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8075,7 +8075,7 @@
         <v>133825706</v>
       </c>
       <c r="B64" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8193,45 +8193,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133825700</v>
+        <v>133825703</v>
       </c>
       <c r="B65" t="n">
-        <v>96358</v>
+        <v>79727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2809</v>
+        <v>257107</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444713</v>
+        <v>444737</v>
       </c>
       <c r="R65" t="n">
-        <v>7025498</v>
+        <v>7025451</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8263,7 +8266,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8273,12 +8276,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8287,8 +8290,24 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8305,48 +8324,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133825703</v>
+        <v>133825700</v>
       </c>
       <c r="B66" t="n">
-        <v>79713</v>
+        <v>96386</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>257107</v>
+        <v>2809</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444737</v>
+        <v>444713</v>
       </c>
       <c r="R66" t="n">
-        <v>7025451</v>
+        <v>7025498</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8378,7 +8394,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8388,12 +8404,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8402,24 +8418,8 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8439,7 +8439,7 @@
         <v>133825702</v>
       </c>
       <c r="B67" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8557,32 +8557,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825713</v>
+        <v>133825711</v>
       </c>
       <c r="B68" t="n">
-        <v>92651</v>
+        <v>83324</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444671</v>
+        <v>444718</v>
       </c>
       <c r="R68" t="n">
-        <v>7025477</v>
+        <v>7025467</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8656,17 +8656,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8684,32 +8684,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825711</v>
+        <v>133825708</v>
       </c>
       <c r="B69" t="n">
-        <v>83310</v>
+        <v>91947</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444718</v>
+        <v>444731</v>
       </c>
       <c r="R69" t="n">
-        <v>7025467</v>
+        <v>7025449</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8783,17 +8783,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8811,45 +8811,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825708</v>
+        <v>133825701</v>
       </c>
       <c r="B70" t="n">
-        <v>91928</v>
+        <v>99168</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444731</v>
+        <v>444721</v>
       </c>
       <c r="R70" t="n">
-        <v>7025449</v>
+        <v>7025487</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8881,7 +8890,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8891,12 +8900,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8907,21 +8916,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8938,10 +8932,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133825701</v>
+        <v>133825707</v>
       </c>
       <c r="B71" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8968,7 +8962,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8982,10 +8976,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444721</v>
+        <v>444725</v>
       </c>
       <c r="R71" t="n">
-        <v>7025487</v>
+        <v>7025460</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9017,7 +9011,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9027,12 +9021,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>8 skott inom 1x1 m i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9059,54 +9053,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133825707</v>
+        <v>133825713</v>
       </c>
       <c r="B72" t="n">
-        <v>99140</v>
+        <v>92172</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444725</v>
+        <v>444671</v>
       </c>
       <c r="R72" t="n">
-        <v>7025460</v>
+        <v>7025477</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9138,7 +9123,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9148,12 +9133,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>8 skott inom 1x1 m i gammal granskog</t>
+          <t>På grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9164,6 +9149,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9183,7 +9183,7 @@
         <v>133825718</v>
       </c>
       <c r="B73" t="n">
-        <v>92888</v>
+        <v>92916</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>133825717</v>
       </c>
       <c r="B74" t="n">
-        <v>101348</v>
+        <v>101376</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>133825710</v>
       </c>
       <c r="B75" t="n">
-        <v>83302</v>
+        <v>83316</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>133825712</v>
       </c>
       <c r="B76" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>133825705</v>
       </c>
       <c r="B77" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>130800360</v>
       </c>
       <c r="B78" t="n">
-        <v>75426</v>
+        <v>75437</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8075,7 +8075,7 @@
         <v>133825706</v>
       </c>
       <c r="B64" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>133825703</v>
       </c>
       <c r="B65" t="n">
-        <v>79727</v>
+        <v>79737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>133825700</v>
       </c>
       <c r="B66" t="n">
-        <v>96386</v>
+        <v>96396</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>133825702</v>
       </c>
       <c r="B67" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>133825711</v>
       </c>
       <c r="B68" t="n">
-        <v>83324</v>
+        <v>83334</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>133825708</v>
       </c>
       <c r="B69" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>133825701</v>
       </c>
       <c r="B70" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>133825707</v>
       </c>
       <c r="B71" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>133825713</v>
       </c>
       <c r="B72" t="n">
-        <v>92172</v>
+        <v>92182</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>133825718</v>
       </c>
       <c r="B73" t="n">
-        <v>92916</v>
+        <v>92926</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>133825717</v>
       </c>
       <c r="B74" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>133825710</v>
       </c>
       <c r="B75" t="n">
-        <v>83316</v>
+        <v>83326</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>133825712</v>
       </c>
       <c r="B76" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>133825705</v>
       </c>
       <c r="B77" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>130800360</v>
       </c>
       <c r="B78" t="n">
-        <v>75437</v>
+        <v>75447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8557,10 +8557,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825711</v>
+        <v>133825701</v>
       </c>
       <c r="B68" t="n">
-        <v>83334</v>
+        <v>99178</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8568,34 +8568,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444718</v>
+        <v>444721</v>
       </c>
       <c r="R68" t="n">
-        <v>7025467</v>
+        <v>7025487</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8627,7 +8636,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8637,12 +8646,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8653,21 +8662,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8684,32 +8678,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825708</v>
+        <v>133825711</v>
       </c>
       <c r="B69" t="n">
-        <v>91957</v>
+        <v>83334</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8719,10 +8713,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444731</v>
+        <v>444718</v>
       </c>
       <c r="R69" t="n">
-        <v>7025449</v>
+        <v>7025467</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8754,7 +8748,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8764,12 +8758,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8783,17 +8777,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8811,54 +8805,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825701</v>
+        <v>133825708</v>
       </c>
       <c r="B70" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444721</v>
+        <v>444731</v>
       </c>
       <c r="R70" t="n">
-        <v>7025487</v>
+        <v>7025449</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8890,7 +8875,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8900,12 +8885,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8916,6 +8901,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8557,10 +8557,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825701</v>
+        <v>133825711</v>
       </c>
       <c r="B68" t="n">
-        <v>99178</v>
+        <v>83334</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8568,43 +8568,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444721</v>
+        <v>444718</v>
       </c>
       <c r="R68" t="n">
-        <v>7025487</v>
+        <v>7025467</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8636,7 +8627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8646,12 +8637,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8662,6 +8653,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8678,32 +8684,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825711</v>
+        <v>133825708</v>
       </c>
       <c r="B69" t="n">
-        <v>83334</v>
+        <v>91957</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8713,10 +8719,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444718</v>
+        <v>444731</v>
       </c>
       <c r="R69" t="n">
-        <v>7025467</v>
+        <v>7025449</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8748,7 +8754,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8758,12 +8764,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8777,17 +8783,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8805,45 +8811,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825708</v>
+        <v>133825701</v>
       </c>
       <c r="B70" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444731</v>
+        <v>444721</v>
       </c>
       <c r="R70" t="n">
-        <v>7025449</v>
+        <v>7025487</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8875,7 +8890,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8885,12 +8900,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8901,21 +8916,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8075,7 +8075,7 @@
         <v>133825706</v>
       </c>
       <c r="B64" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8193,48 +8193,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133825703</v>
+        <v>133825700</v>
       </c>
       <c r="B65" t="n">
-        <v>79737</v>
+        <v>96398</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>257107</v>
+        <v>2809</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444737</v>
+        <v>444713</v>
       </c>
       <c r="R65" t="n">
-        <v>7025451</v>
+        <v>7025498</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8266,7 +8263,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8276,12 +8273,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8290,24 +8287,8 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8324,45 +8305,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133825700</v>
+        <v>133825703</v>
       </c>
       <c r="B66" t="n">
-        <v>96396</v>
+        <v>79738</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>257107</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444713</v>
+        <v>444737</v>
       </c>
       <c r="R66" t="n">
-        <v>7025498</v>
+        <v>7025451</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8394,7 +8378,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8404,12 +8388,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8418,8 +8402,24 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8439,7 +8439,7 @@
         <v>133825702</v>
       </c>
       <c r="B67" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8557,10 +8557,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825711</v>
+        <v>133825707</v>
       </c>
       <c r="B68" t="n">
-        <v>83334</v>
+        <v>99180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8568,34 +8568,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444718</v>
+        <v>444725</v>
       </c>
       <c r="R68" t="n">
-        <v>7025467</v>
+        <v>7025460</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8627,7 +8636,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8637,12 +8646,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>8 skott inom 1x1 m i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8653,21 +8662,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8684,32 +8678,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825708</v>
+        <v>133825713</v>
       </c>
       <c r="B69" t="n">
-        <v>91957</v>
+        <v>92184</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8719,10 +8713,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444731</v>
+        <v>444671</v>
       </c>
       <c r="R69" t="n">
-        <v>7025449</v>
+        <v>7025477</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8754,7 +8748,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8764,12 +8758,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>På grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8811,10 +8805,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825701</v>
+        <v>133825711</v>
       </c>
       <c r="B70" t="n">
-        <v>99178</v>
+        <v>83335</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8822,43 +8816,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>492</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444721</v>
+        <v>444718</v>
       </c>
       <c r="R70" t="n">
-        <v>7025487</v>
+        <v>7025467</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8890,7 +8875,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8900,12 +8885,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8916,6 +8901,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8932,54 +8932,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133825707</v>
+        <v>133825708</v>
       </c>
       <c r="B71" t="n">
-        <v>99178</v>
+        <v>91959</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444725</v>
+        <v>444731</v>
       </c>
       <c r="R71" t="n">
-        <v>7025460</v>
+        <v>7025449</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9011,7 +9002,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9021,12 +9012,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>8 skott inom 1x1 m i gammal granskog</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9037,6 +9028,21 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9053,45 +9059,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133825713</v>
+        <v>133825701</v>
       </c>
       <c r="B72" t="n">
-        <v>92182</v>
+        <v>99180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444671</v>
+        <v>444721</v>
       </c>
       <c r="R72" t="n">
-        <v>7025477</v>
+        <v>7025487</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9123,7 +9138,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9133,12 +9148,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9149,21 +9164,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9183,7 +9183,7 @@
         <v>133825718</v>
       </c>
       <c r="B73" t="n">
-        <v>92926</v>
+        <v>92928</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>133825717</v>
       </c>
       <c r="B74" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>133825710</v>
       </c>
       <c r="B75" t="n">
-        <v>83326</v>
+        <v>83327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>133825712</v>
       </c>
       <c r="B76" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>133825705</v>
       </c>
       <c r="B77" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8193,45 +8193,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133825700</v>
+        <v>133825703</v>
       </c>
       <c r="B65" t="n">
-        <v>96398</v>
+        <v>79738</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2809</v>
+        <v>257107</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444713</v>
+        <v>444737</v>
       </c>
       <c r="R65" t="n">
-        <v>7025498</v>
+        <v>7025451</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8263,7 +8266,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8273,12 +8276,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8287,8 +8290,24 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8305,48 +8324,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133825703</v>
+        <v>133825700</v>
       </c>
       <c r="B66" t="n">
-        <v>79738</v>
+        <v>96398</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>257107</v>
+        <v>2809</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444737</v>
+        <v>444713</v>
       </c>
       <c r="R66" t="n">
-        <v>7025451</v>
+        <v>7025498</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8378,7 +8394,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8388,12 +8404,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8402,24 +8418,8 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8557,10 +8557,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825707</v>
+        <v>133825711</v>
       </c>
       <c r="B68" t="n">
-        <v>99180</v>
+        <v>83335</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8568,43 +8568,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444725</v>
+        <v>444718</v>
       </c>
       <c r="R68" t="n">
-        <v>7025460</v>
+        <v>7025467</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8636,7 +8627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8646,12 +8637,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>8 skott inom 1x1 m i gammal granskog</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8662,6 +8653,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8678,32 +8684,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825713</v>
+        <v>133825708</v>
       </c>
       <c r="B69" t="n">
-        <v>92184</v>
+        <v>91959</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8713,10 +8719,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444671</v>
+        <v>444731</v>
       </c>
       <c r="R69" t="n">
-        <v>7025477</v>
+        <v>7025449</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8748,7 +8754,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8758,12 +8764,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8805,10 +8811,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825711</v>
+        <v>133825701</v>
       </c>
       <c r="B70" t="n">
-        <v>83335</v>
+        <v>99180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8816,34 +8822,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>492</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444718</v>
+        <v>444721</v>
       </c>
       <c r="R70" t="n">
-        <v>7025467</v>
+        <v>7025487</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8875,7 +8890,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8885,12 +8900,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8901,21 +8916,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8932,45 +8932,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133825708</v>
+        <v>133825707</v>
       </c>
       <c r="B71" t="n">
-        <v>91959</v>
+        <v>99180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444731</v>
+        <v>444725</v>
       </c>
       <c r="R71" t="n">
-        <v>7025449</v>
+        <v>7025460</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9002,7 +9011,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9012,12 +9021,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>8 skott inom 1x1 m i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9028,21 +9037,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9059,54 +9053,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133825701</v>
+        <v>133825713</v>
       </c>
       <c r="B72" t="n">
-        <v>99180</v>
+        <v>92184</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444721</v>
+        <v>444671</v>
       </c>
       <c r="R72" t="n">
-        <v>7025487</v>
+        <v>7025477</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9138,7 +9123,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9148,12 +9133,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>På grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9164,6 +9149,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8557,32 +8557,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825713</v>
+        <v>133825711</v>
       </c>
       <c r="B68" t="n">
-        <v>92185</v>
+        <v>83335</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444671</v>
+        <v>444718</v>
       </c>
       <c r="R68" t="n">
-        <v>7025477</v>
+        <v>7025467</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8656,17 +8656,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8684,54 +8684,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825707</v>
+        <v>133825708</v>
       </c>
       <c r="B69" t="n">
-        <v>99181</v>
+        <v>91960</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444725</v>
+        <v>444731</v>
       </c>
       <c r="R69" t="n">
-        <v>7025460</v>
+        <v>7025449</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8763,7 +8754,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8773,12 +8764,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>8 skott inom 1x1 m i gammal granskog</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8789,6 +8780,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8805,45 +8811,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825708</v>
+        <v>133825701</v>
       </c>
       <c r="B70" t="n">
-        <v>91960</v>
+        <v>99181</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444731</v>
+        <v>444721</v>
       </c>
       <c r="R70" t="n">
-        <v>7025449</v>
+        <v>7025487</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8875,7 +8890,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8885,12 +8900,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8901,21 +8916,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8932,10 +8932,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133825711</v>
+        <v>133825707</v>
       </c>
       <c r="B71" t="n">
-        <v>83335</v>
+        <v>99181</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8943,34 +8943,43 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>492</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444718</v>
+        <v>444725</v>
       </c>
       <c r="R71" t="n">
-        <v>7025467</v>
+        <v>7025460</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9002,7 +9011,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9012,12 +9021,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>8 skott inom 1x1 m i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9028,21 +9037,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9059,54 +9053,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133825701</v>
+        <v>133825713</v>
       </c>
       <c r="B72" t="n">
-        <v>99181</v>
+        <v>92185</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444721</v>
+        <v>444671</v>
       </c>
       <c r="R72" t="n">
-        <v>7025487</v>
+        <v>7025477</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9138,7 +9123,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9148,12 +9133,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>På grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9164,6 +9149,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -8075,7 +8075,7 @@
         <v>133825706</v>
       </c>
       <c r="B64" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>133825703</v>
       </c>
       <c r="B65" t="n">
-        <v>79738</v>
+        <v>79745</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>133825700</v>
       </c>
       <c r="B66" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>133825702</v>
       </c>
       <c r="B67" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>133825711</v>
       </c>
       <c r="B68" t="n">
-        <v>83335</v>
+        <v>83342</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8684,45 +8684,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825708</v>
+        <v>133825701</v>
       </c>
       <c r="B69" t="n">
-        <v>91960</v>
+        <v>99188</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444731</v>
+        <v>444721</v>
       </c>
       <c r="R69" t="n">
-        <v>7025449</v>
+        <v>7025487</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8754,7 +8763,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8764,12 +8773,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8780,21 +8789,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8811,54 +8805,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825701</v>
+        <v>133825713</v>
       </c>
       <c r="B70" t="n">
-        <v>99181</v>
+        <v>92192</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444721</v>
+        <v>444671</v>
       </c>
       <c r="R70" t="n">
-        <v>7025487</v>
+        <v>7025477</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8890,7 +8875,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8900,12 +8885,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>På grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8916,6 +8901,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8932,54 +8932,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133825707</v>
+        <v>133825708</v>
       </c>
       <c r="B71" t="n">
-        <v>99181</v>
+        <v>91967</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444725</v>
+        <v>444731</v>
       </c>
       <c r="R71" t="n">
-        <v>7025460</v>
+        <v>7025449</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9011,7 +9002,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9021,12 +9012,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>8 skott inom 1x1 m i gammal granskog</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9037,6 +9028,21 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9053,45 +9059,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133825713</v>
+        <v>133825707</v>
       </c>
       <c r="B72" t="n">
-        <v>92185</v>
+        <v>99188</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444671</v>
+        <v>444725</v>
       </c>
       <c r="R72" t="n">
-        <v>7025477</v>
+        <v>7025460</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9123,7 +9138,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9133,12 +9148,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe</t>
+          <t>8 skott inom 1x1 m i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9149,21 +9164,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9183,7 +9183,7 @@
         <v>133825718</v>
       </c>
       <c r="B73" t="n">
-        <v>92929</v>
+        <v>92936</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>133825717</v>
       </c>
       <c r="B74" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>133825710</v>
       </c>
       <c r="B75" t="n">
-        <v>83327</v>
+        <v>83334</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>133825712</v>
       </c>
       <c r="B76" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>133825705</v>
       </c>
       <c r="B77" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>130800360</v>
       </c>
       <c r="B78" t="n">
-        <v>75447</v>
+        <v>75454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130330846</v>
+        <v>130812174</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>83302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444588</v>
+        <v>444717</v>
       </c>
       <c r="R2" t="n">
-        <v>7025515</v>
+        <v>7025526</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på gammal gran nära dike</t>
+          <t>på bark på stam av gammal lutande, levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +771,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,45 +802,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330856</v>
+        <v>130800375</v>
       </c>
       <c r="B3" t="n">
-        <v>80327</v>
+        <v>83298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444718</v>
+        <v>444662</v>
       </c>
       <c r="R3" t="n">
-        <v>7025527</v>
+        <v>7025556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,27 +867,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +898,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,45 +929,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130330831</v>
+        <v>133825711</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>83349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444731</v>
+        <v>444718</v>
       </c>
       <c r="R4" t="n">
-        <v>7025453</v>
+        <v>7025467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,27 +994,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal barrblandskog</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,6 +1025,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1004,17 +1049,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330860</v>
+        <v>130330848</v>
       </c>
       <c r="B5" t="n">
-        <v>80326</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1067,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444738</v>
+        <v>444573</v>
       </c>
       <c r="R5" t="n">
-        <v>7025522</v>
+        <v>7025542</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
+          <t>på död stående gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130330857</v>
+        <v>130330852</v>
       </c>
       <c r="B6" t="n">
-        <v>80326</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1179,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444718</v>
+        <v>444675</v>
       </c>
       <c r="R6" t="n">
-        <v>7025527</v>
+        <v>7025575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på gammal lutande sälg i gammal granskog</t>
+          <t>på granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130330824</v>
+        <v>130800353</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,34 +1291,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444645</v>
+        <v>444652</v>
       </c>
       <c r="R7" t="n">
-        <v>7025385</v>
+        <v>7025557</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,27 +1345,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
+          <t>På bark vid basen av gammal levande gran (41 cm dbh, ca 175 år ) i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,6 +1376,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1347,45 +1407,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130330836</v>
+        <v>133825708</v>
       </c>
       <c r="B8" t="n">
-        <v>80355</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444722</v>
+        <v>444731</v>
       </c>
       <c r="R8" t="n">
-        <v>7025477</v>
+        <v>7025449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,27 +1472,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg i gammal (150-200 år) barrblandskog</t>
+          <t>På klen gammal granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,6 +1503,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1452,52 +1527,52 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130330828</v>
+        <v>133825712</v>
       </c>
       <c r="B9" t="n">
-        <v>80362</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444731</v>
+        <v>444721</v>
       </c>
       <c r="R9" t="n">
-        <v>7025453</v>
+        <v>7025472</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,27 +1599,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på gammal sälg i gammal barrblandskog</t>
+          <t>På gammal granlåga i gammal granskog med tallöverståndare</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,6 +1630,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1564,17 +1654,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130330834</v>
+        <v>130800361</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>75412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1672,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444722</v>
+        <v>444731</v>
       </c>
       <c r="R10" t="n">
-        <v>7025477</v>
+        <v>7025516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,27 +1726,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,6 +1757,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1683,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130330852</v>
+        <v>130330845</v>
       </c>
       <c r="B11" t="n">
-        <v>91772</v>
+        <v>83312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1799,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444675</v>
+        <v>444588</v>
       </c>
       <c r="R11" t="n">
-        <v>7025575</v>
+        <v>7025517</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på granhögstubbe i gammal granskog</t>
+          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,45 +1900,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130330843</v>
+        <v>130800360</v>
       </c>
       <c r="B12" t="n">
-        <v>75199</v>
+        <v>75461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>1776</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444588</v>
+        <v>444731</v>
       </c>
       <c r="R12" t="n">
-        <v>7025517</v>
+        <v>7025516</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,37 +1965,52 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>på döda grenar på  grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1910,7 +2030,7 @@
         <v>130330830</v>
       </c>
       <c r="B13" t="n">
-        <v>80327</v>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130330837</v>
+        <v>130330835</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2150,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2251,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130330835</v>
+        <v>130330856</v>
       </c>
       <c r="B15" t="n">
-        <v>80327</v>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,10 +2286,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444722</v>
+        <v>444718</v>
       </c>
       <c r="R15" t="n">
-        <v>7025477</v>
+        <v>7025527</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2321,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,12 +2331,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg i gammal (150-200 år) barrblandskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130330858</v>
+        <v>130330859</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,43 +2374,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444728</v>
+        <v>444738</v>
       </c>
       <c r="R16" t="n">
-        <v>7025532</v>
+        <v>7025522</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
+          <t>På två sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2475,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130330839</v>
+        <v>130800356</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,34 +2486,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444650</v>
+        <v>444731</v>
       </c>
       <c r="R17" t="n">
-        <v>7025524</v>
+        <v>7025516</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,27 +2540,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
+          <t>På bark av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,6 +2571,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2476,45 +2602,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130330840</v>
+        <v>133825700</v>
       </c>
       <c r="B18" t="n">
-        <v>79221</v>
+        <v>96413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444637</v>
+        <v>444713</v>
       </c>
       <c r="R18" t="n">
-        <v>7025502</v>
+        <v>7025498</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,27 +2667,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,17 +2707,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130330823</v>
+        <v>133825716</v>
       </c>
       <c r="B19" t="n">
-        <v>97845</v>
+        <v>96410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,34 +2725,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>2812</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444645</v>
+        <v>444683</v>
       </c>
       <c r="R19" t="n">
-        <v>7025385</v>
+        <v>7025604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,27 +2779,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på marken i gammal granskog</t>
+          <t>På marken längs bäck</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,52 +2819,52 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130330826</v>
+        <v>133825713</v>
       </c>
       <c r="B20" t="n">
-        <v>79221</v>
+        <v>92199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444727</v>
+        <v>444671</v>
       </c>
       <c r="R20" t="n">
-        <v>7025514</v>
+        <v>7025477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2765,27 +2891,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>På grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,6 +2922,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2805,52 +2946,52 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130330825</v>
+        <v>133825718</v>
       </c>
       <c r="B21" t="n">
-        <v>79221</v>
+        <v>92943</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444715</v>
+        <v>444672</v>
       </c>
       <c r="R21" t="n">
-        <v>7025456</v>
+        <v>7025569</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2877,27 +3018,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>I gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2917,39 +3058,39 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130330841</v>
+        <v>130330822</v>
       </c>
       <c r="B22" t="n">
-        <v>78233</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,10 +3100,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444637</v>
+        <v>444629</v>
       </c>
       <c r="R22" t="n">
-        <v>7025502</v>
+        <v>7025390</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,7 +3135,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,12 +3145,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
+          <t>på gammal levande gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,14 +3177,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130330854</v>
+        <v>130330824</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3071,10 +3212,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444673</v>
+        <v>444645</v>
       </c>
       <c r="R23" t="n">
-        <v>7025591</v>
+        <v>7025385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3106,7 +3247,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3116,12 +3257,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på gammal grov gran vid bäck</t>
+          <t>rikligt på gammal levande gran i gammal granskog, längsta bål 45 cm</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,30 +3289,34 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130330842</v>
+        <v>130330825</v>
       </c>
       <c r="B24" t="n">
-        <v>91796</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3179,10 +3324,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444550</v>
+        <v>444715</v>
       </c>
       <c r="R24" t="n">
-        <v>7025500</v>
+        <v>7025456</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,7 +3359,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,12 +3369,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,30 +3401,34 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130330851</v>
+        <v>130330826</v>
       </c>
       <c r="B25" t="n">
-        <v>91796</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3287,10 +3436,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444607</v>
+        <v>444727</v>
       </c>
       <c r="R25" t="n">
-        <v>7025579</v>
+        <v>7025514</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3322,7 +3471,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3332,12 +3481,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>på död stående gran vid dike/bäck</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,32 +3513,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130330833</v>
+        <v>130330831</v>
       </c>
       <c r="B26" t="n">
-        <v>80230</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3449,7 +3598,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>på gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,32 +3625,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130330827</v>
+        <v>130330834</v>
       </c>
       <c r="B27" t="n">
-        <v>80326</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,10 +3660,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444727</v>
+        <v>444722</v>
       </c>
       <c r="R27" t="n">
-        <v>7025514</v>
+        <v>7025477</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3546,7 +3695,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3556,12 +3705,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande sälg i gammal granskog</t>
+          <t>på gammal gran i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3588,30 +3737,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130330847</v>
+        <v>130330838</v>
       </c>
       <c r="B28" t="n">
-        <v>91796</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3619,10 +3772,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444564</v>
+        <v>444683</v>
       </c>
       <c r="R28" t="n">
-        <v>7025540</v>
+        <v>7025492</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3654,7 +3807,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3664,12 +3817,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>på död gran (ca 170 år, 22 cm dbh) i gammal granskog nära dike</t>
+          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3696,32 +3849,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130330848</v>
+        <v>130330839</v>
       </c>
       <c r="B29" t="n">
-        <v>91772</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3731,10 +3884,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444573</v>
+        <v>444650</v>
       </c>
       <c r="R29" t="n">
-        <v>7025542</v>
+        <v>7025524</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,7 +3919,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3776,12 +3929,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>på död stående gran i gammal granskog</t>
+          <t>på gammal gran (närmare 200 år) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3808,14 +3961,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130330822</v>
+        <v>130330840</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3843,10 +3996,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444629</v>
+        <v>444637</v>
       </c>
       <c r="R30" t="n">
-        <v>7025390</v>
+        <v>7025502</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +4031,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,12 +4041,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på gammal levande gran i gammal barrblandskog</t>
+          <t>på  levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,32 +4073,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130330845</v>
+        <v>130330846</v>
       </c>
       <c r="B31" t="n">
-        <v>83206</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3958,7 +4111,7 @@
         <v>444588</v>
       </c>
       <c r="R31" t="n">
-        <v>7025517</v>
+        <v>7025515</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +4143,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,12 +4153,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>rikligt vid basen av grov gammal gran (60 cm dbh) i gammal granskog</t>
+          <t>på gammal gran nära dike</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4032,14 +4185,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130330838</v>
+        <v>130330854</v>
       </c>
       <c r="B32" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4067,10 +4220,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444683</v>
+        <v>444673</v>
       </c>
       <c r="R32" t="n">
-        <v>7025492</v>
+        <v>7025591</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4255,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,12 +4265,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>rikligt på gammal levande gran i gammal (200-årig) barrblandskog</t>
+          <t>på gammal grov gran vid bäck</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,45 +4297,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130330859</v>
+        <v>130330855</v>
       </c>
       <c r="B33" t="n">
-        <v>80327</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444738</v>
+        <v>444696</v>
       </c>
       <c r="R33" t="n">
-        <v>7025522</v>
+        <v>7025558</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4376,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4386,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På två sälgar i kanten av gammal barrblandskog</t>
+          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,41 +4418,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330849</v>
+        <v>130330858</v>
       </c>
       <c r="B34" t="n">
-        <v>91796</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444569</v>
+        <v>444728</v>
       </c>
       <c r="R34" t="n">
-        <v>7025541</v>
+        <v>7025532</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4497,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,12 +4507,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på grov granhögstubbe i gammal granskog nära dike</t>
+          <t>Längsta bål 40 cm, på ca 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,14 +4539,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330855</v>
+        <v>130795187</v>
       </c>
       <c r="B35" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4394,7 +4569,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4404,17 +4579,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444696</v>
+        <v>444732</v>
       </c>
       <c r="R35" t="n">
-        <v>7025558</v>
+        <v>7025497</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4438,27 +4613,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på 200-årig tall, längsta bål 50 cm, i gammal barrblandskog</t>
+          <t>På gammal tall i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,6 +4644,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4485,45 +4675,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130330850</v>
+        <v>130795639</v>
       </c>
       <c r="B36" t="n">
-        <v>83201</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444566</v>
+        <v>444689</v>
       </c>
       <c r="R36" t="n">
-        <v>7025535</v>
+        <v>7025495</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4550,27 +4749,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på ca 175 år gammal levande gran (30 cm dbh) i gammal granskog med inslag av glasbjörk och tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4581,6 +4780,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4597,45 +4811,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130330832</v>
+        <v>130800351</v>
       </c>
       <c r="B37" t="n">
-        <v>80326</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444731</v>
+        <v>444702</v>
       </c>
       <c r="R37" t="n">
-        <v>7025453</v>
+        <v>7025492</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4662,27 +4885,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Rikligt, minst 50 bålar på gammal levande tall (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4693,6 +4916,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4709,67 +4947,51 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130795562</v>
+        <v>130800352</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444696</v>
+        <v>444700</v>
       </c>
       <c r="R38" t="n">
-        <v>7025469</v>
+        <v>7025517</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4798,7 +5020,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4808,12 +5030,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Hördes först födosöka flög sedan till grantopp och hördes sedan locka några meter norrut</t>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4822,8 +5044,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4840,14 +5078,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800368</v>
+        <v>130800354</v>
       </c>
       <c r="B39" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4875,10 +5113,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444705</v>
+        <v>444716</v>
       </c>
       <c r="R39" t="n">
-        <v>7025565</v>
+        <v>7025439</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4910,7 +5148,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4920,12 +5158,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt på gammal död gran i gammal granskog, även troliga ringhack</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4967,32 +5205,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130800353</v>
+        <v>130800355</v>
       </c>
       <c r="B40" t="n">
-        <v>91804</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5002,10 +5240,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444652</v>
+        <v>444716</v>
       </c>
       <c r="R40" t="n">
-        <v>7025557</v>
+        <v>7025474</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5037,7 +5275,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5047,12 +5285,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran (41 cm dbh, ca 175 år ) i gammal granskog</t>
+          <t>På gammal tall med pansarbark, längsta bål 40 cm, i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5066,17 +5304,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5094,14 +5332,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800376</v>
+        <v>130800367</v>
       </c>
       <c r="B41" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5122,17 +5360,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444675</v>
+        <v>444721</v>
       </c>
       <c r="R41" t="n">
-        <v>7025530</v>
+        <v>7025542</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5164,7 +5411,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5174,12 +5421,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På levande gammal gran i gammal granskog</t>
+          <t>200 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5221,32 +5468,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800366</v>
+        <v>130800368</v>
       </c>
       <c r="B42" t="n">
-        <v>78255</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5256,10 +5503,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444721</v>
+        <v>444705</v>
       </c>
       <c r="R42" t="n">
-        <v>7025542</v>
+        <v>7025565</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5291,7 +5538,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5301,12 +5548,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal död gran i gammal granskog, även troliga ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5348,45 +5595,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800374</v>
+        <v>130800369</v>
       </c>
       <c r="B43" t="n">
-        <v>83206</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444662</v>
+        <v>444704</v>
       </c>
       <c r="R43" t="n">
-        <v>7025556</v>
+        <v>7025567</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5418,7 +5674,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5428,12 +5684,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+          <t>80 bålar på gammal levande tall (ca 200 år, 23 cm dbh) i gles gammal barrblandskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5447,17 +5703,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5475,14 +5731,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130795187</v>
+        <v>130800372</v>
       </c>
       <c r="B44" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5503,29 +5759,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444732</v>
+        <v>444688</v>
       </c>
       <c r="R44" t="n">
-        <v>7025497</v>
+        <v>7025582</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5554,7 +5801,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5564,12 +5811,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal tall i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5583,17 +5830,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5611,32 +5858,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800370</v>
+        <v>130800376</v>
       </c>
       <c r="B45" t="n">
-        <v>75221</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5646,10 +5893,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444683</v>
+        <v>444675</v>
       </c>
       <c r="R45" t="n">
-        <v>7025584</v>
+        <v>7025530</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5681,7 +5928,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5691,12 +5938,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På ved på gren på gammal levande gran i gammal granskog</t>
+          <t>På levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5738,45 +5985,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130795383</v>
+        <v>130330843</v>
       </c>
       <c r="B46" t="n">
-        <v>80348</v>
+        <v>75300</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444726</v>
+        <v>444588</v>
       </c>
       <c r="R46" t="n">
-        <v>7025453</v>
+        <v>7025517</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5803,27 +6050,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal klen sälg i gammal barrblandskog</t>
+          <t>på döda grenar på  grov gammal gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5834,21 +6081,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5865,32 +6097,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130800372</v>
+        <v>130800359</v>
       </c>
       <c r="B47" t="n">
-        <v>79243</v>
+        <v>75300</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5900,10 +6132,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444688</v>
+        <v>444731</v>
       </c>
       <c r="R47" t="n">
-        <v>7025582</v>
+        <v>7025516</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5935,7 +6167,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5945,12 +6177,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5964,17 +6196,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5992,54 +6224,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130795639</v>
+        <v>130800370</v>
       </c>
       <c r="B48" t="n">
-        <v>79243</v>
+        <v>75300</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Litnersmyren, Litnersmyren, Jmt</t>
+          <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444689</v>
+        <v>444683</v>
       </c>
       <c r="R48" t="n">
-        <v>7025495</v>
+        <v>7025584</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6071,7 +6294,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6081,12 +6304,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt på ca 175 år gammal levande gran (30 cm dbh) i gammal granskog med inslag av glasbjörk och tall</t>
+          <t>På ved på gren på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6128,32 +6351,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130800378</v>
+        <v>130800374</v>
       </c>
       <c r="B49" t="n">
-        <v>78255</v>
+        <v>83290</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6163,10 +6386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444675</v>
+        <v>444662</v>
       </c>
       <c r="R49" t="n">
-        <v>7025530</v>
+        <v>7025556</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6198,7 +6421,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6208,12 +6431,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6227,17 +6450,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6255,32 +6478,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130800355</v>
+        <v>133825710</v>
       </c>
       <c r="B50" t="n">
-        <v>79243</v>
+        <v>83341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6290,10 +6513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444716</v>
+        <v>444718</v>
       </c>
       <c r="R50" t="n">
-        <v>7025474</v>
+        <v>7025467</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6320,27 +6543,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal tall med pansarbark, längsta bål 40 cm, i gammal granskog</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6354,17 +6577,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6375,17 +6598,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130800369</v>
+        <v>130330850</v>
       </c>
       <c r="B51" t="n">
-        <v>79243</v>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6393,43 +6616,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444704</v>
+        <v>444566</v>
       </c>
       <c r="R51" t="n">
-        <v>7025567</v>
+        <v>7025535</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6456,27 +6670,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>80 bålar på gammal levande tall (ca 200 år, 23 cm dbh) i gles gammal barrblandskog, längsta bål 40 cm</t>
+          <t>på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6487,21 +6701,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6518,10 +6717,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130800359</v>
+        <v>130330833</v>
       </c>
       <c r="B52" t="n">
-        <v>75221</v>
+        <v>80336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6529,34 +6728,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6428</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
         <v>444731</v>
       </c>
       <c r="R52" t="n">
-        <v>7025516</v>
+        <v>7025453</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6583,27 +6782,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>på bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6614,21 +6813,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6645,10 +6829,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130800367</v>
+        <v>130330827</v>
       </c>
       <c r="B53" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6656,43 +6840,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444721</v>
+        <v>444727</v>
       </c>
       <c r="R53" t="n">
-        <v>7025542</v>
+        <v>7025514</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6719,27 +6894,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>200 bålar på gammal levande gran i gammal granskog</t>
+          <t>rikligt på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6750,21 +6925,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6781,10 +6941,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130800352</v>
+        <v>130330829</v>
       </c>
       <c r="B54" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6792,37 +6952,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444700</v>
+        <v>444731</v>
       </c>
       <c r="R54" t="n">
-        <v>7025517</v>
+        <v>7025453</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6849,27 +7006,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>på två gamla sälgar i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6878,24 +7035,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6912,45 +7053,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130800375</v>
+        <v>130330837</v>
       </c>
       <c r="B55" t="n">
-        <v>83214</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444662</v>
+        <v>444722</v>
       </c>
       <c r="R55" t="n">
-        <v>7025556</v>
+        <v>7025477</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6977,27 +7118,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Vid basen av grov björkhögstubbe (30 cm dbh) i gammal granskog med inslag av tallöverståndare</t>
+          <t>på bark på stam av levande gammal sälg i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7008,21 +7149,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7039,45 +7165,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130800364</v>
+        <v>130330857</v>
       </c>
       <c r="B56" t="n">
-        <v>80384</v>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444717</v>
+        <v>444718</v>
       </c>
       <c r="R56" t="n">
-        <v>7025526</v>
+        <v>7025527</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7104,27 +7230,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
+          <t>på gammal lutande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7135,21 +7261,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7166,10 +7277,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130800354</v>
+        <v>130330860</v>
       </c>
       <c r="B57" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7177,34 +7288,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444716</v>
+        <v>444738</v>
       </c>
       <c r="R57" t="n">
-        <v>7025439</v>
+        <v>7025522</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7231,27 +7342,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>rikligt på 4 gamla sälgar i kanten av gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7262,21 +7373,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7293,10 +7389,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130800361</v>
+        <v>130795383</v>
       </c>
       <c r="B58" t="n">
-        <v>75333</v>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7304,34 +7400,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444731</v>
+        <v>444726</v>
       </c>
       <c r="R58" t="n">
-        <v>7025516</v>
+        <v>7025453</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7363,7 +7459,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7373,12 +7469,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>På gammal klen sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7420,54 +7516,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130800351</v>
+        <v>130330836</v>
       </c>
       <c r="B59" t="n">
-        <v>79243</v>
+        <v>80461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444702</v>
+        <v>444722</v>
       </c>
       <c r="R59" t="n">
-        <v>7025492</v>
+        <v>7025477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7494,27 +7581,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt, minst 50 bålar på gammal levande tall (50 cm dbh) i gammal granskog</t>
+          <t>på bark på stam av levande gammal sälg i gammal (150-200 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7525,21 +7612,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7556,45 +7628,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130800356</v>
+        <v>130330828</v>
       </c>
       <c r="B60" t="n">
-        <v>80349</v>
+        <v>80468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
         <v>444731</v>
       </c>
       <c r="R60" t="n">
-        <v>7025516</v>
+        <v>7025453</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7621,27 +7693,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På bark av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>på gammal sälg i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7652,21 +7724,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7683,32 +7740,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130800371</v>
+        <v>130800364</v>
       </c>
       <c r="B61" t="n">
-        <v>78255</v>
+        <v>80468</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7718,10 +7775,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444684</v>
+        <v>444717</v>
       </c>
       <c r="R61" t="n">
-        <v>7025581</v>
+        <v>7025526</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7753,7 +7810,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7763,12 +7820,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande lutande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7782,17 +7839,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7810,10 +7867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130812174</v>
+        <v>130795562</v>
       </c>
       <c r="B62" t="n">
-        <v>83219</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7821,37 +7878,56 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444717</v>
+        <v>444696</v>
       </c>
       <c r="R62" t="n">
-        <v>7025526</v>
+        <v>7025469</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7880,7 +7956,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7890,12 +7966,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal lutande, levande sälg i gammal granskog</t>
+          <t>Hördes först födosöka flög sedan till grantopp och hördes sedan locka några meter norrut</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7906,21 +7982,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7937,48 +7998,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130800358</v>
+        <v>133825701</v>
       </c>
       <c r="B63" t="n">
-        <v>85150</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229431</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglavshårprick</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Niesslia lobariae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Etayo &amp; Diederich</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444731</v>
+        <v>444721</v>
       </c>
       <c r="R63" t="n">
-        <v>7025516</v>
+        <v>7025487</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8005,27 +8072,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På död/döende lunglav 1,8 m upp på grov gammal levande sälg (50 cm dbh) i gammal granskog. Mikroskoperad, seta bruna, 75 my långa, 6 my närmare basen gradvis avsmalnande, torra perithecier kollapsade enligt bild i Etayo &amp; Diederich 1996.</t>
+          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8034,28 +8101,8 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>lunglav</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8065,17 +8112,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133825706</v>
+        <v>133825702</v>
       </c>
       <c r="B64" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8102,7 +8149,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8116,10 +8163,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444728</v>
+        <v>444726</v>
       </c>
       <c r="R64" t="n">
-        <v>7025454</v>
+        <v>7025477</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8151,7 +8198,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8161,12 +8208,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>115 skott på marken i gammal granskog</t>
+          <t>97 plantor inom 2x2 m i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8193,48 +8240,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133825703</v>
+        <v>133825705</v>
       </c>
       <c r="B65" t="n">
-        <v>79745</v>
+        <v>99195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>257107</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444737</v>
+        <v>444725</v>
       </c>
       <c r="R65" t="n">
-        <v>7025451</v>
+        <v>7025449</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8266,7 +8319,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8276,12 +8329,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>32 skott inom 0,7x0,5 m på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8290,24 +8343,8 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8324,45 +8361,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133825700</v>
+        <v>133825706</v>
       </c>
       <c r="B66" t="n">
-        <v>96406</v>
+        <v>99195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444713</v>
+        <v>444728</v>
       </c>
       <c r="R66" t="n">
-        <v>7025498</v>
+        <v>7025454</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8394,7 +8440,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8404,12 +8450,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>115 skott på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8436,10 +8482,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133825702</v>
+        <v>133825707</v>
       </c>
       <c r="B67" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8466,7 +8512,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8480,10 +8526,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444726</v>
+        <v>444725</v>
       </c>
       <c r="R67" t="n">
-        <v>7025477</v>
+        <v>7025460</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8515,7 +8561,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8525,12 +8571,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>97 plantor inom 2x2 m i gammal granskog</t>
+          <t>8 skott inom 1x1 m i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8557,45 +8603,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133825711</v>
+        <v>130330823</v>
       </c>
       <c r="B68" t="n">
-        <v>83342</v>
+        <v>97983</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444718</v>
+        <v>444645</v>
       </c>
       <c r="R68" t="n">
-        <v>7025467</v>
+        <v>7025385</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8622,27 +8668,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8653,21 +8699,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8677,61 +8708,52 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133825701</v>
+        <v>133825717</v>
       </c>
       <c r="B69" t="n">
-        <v>99188</v>
+        <v>101403</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444721</v>
+        <v>444683</v>
       </c>
       <c r="R69" t="n">
-        <v>7025487</v>
+        <v>7025604</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8763,7 +8785,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8773,12 +8795,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>210 plantor inom 2x2 m i gammal fuktig granskog</t>
+          <t>På marken längs bäck</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8805,10 +8827,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133825713</v>
+        <v>133825704</v>
       </c>
       <c r="B70" t="n">
-        <v>92192</v>
+        <v>101324</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8816,21 +8838,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>222782</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Anemone nemorosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8840,10 +8862,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444671</v>
+        <v>444725</v>
       </c>
       <c r="R70" t="n">
-        <v>7025477</v>
+        <v>7025449</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8875,7 +8897,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8885,12 +8907,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8901,21 +8923,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8932,32 +8939,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133825708</v>
+        <v>133825714</v>
       </c>
       <c r="B71" t="n">
-        <v>91967</v>
+        <v>101324</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>222782</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anemone nemorosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8967,10 +8974,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444731</v>
+        <v>444685</v>
       </c>
       <c r="R71" t="n">
-        <v>7025449</v>
+        <v>7025604</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9002,7 +9009,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9012,12 +9019,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På klen gammal granlåga</t>
+          <t>På marken längs bäck</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9028,21 +9035,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9059,54 +9051,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133825707</v>
+        <v>130330841</v>
       </c>
       <c r="B72" t="n">
-        <v>99188</v>
+        <v>78339</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Litnersmyran, Jmt</t>
+          <t>Litnersmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444725</v>
+        <v>444637</v>
       </c>
       <c r="R72" t="n">
-        <v>7025460</v>
+        <v>7025502</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9133,27 +9116,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>8 skott inom 1x1 m i gammal granskog</t>
+          <t>på bark på stam av levande gammal gran (175 år, 35 cm dbh) i gammal granskog vid bäck</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9173,39 +9156,39 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133825718</v>
+        <v>130800366</v>
       </c>
       <c r="B73" t="n">
-        <v>92936</v>
+        <v>78339</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9215,10 +9198,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444672</v>
+        <v>444721</v>
       </c>
       <c r="R73" t="n">
-        <v>7025569</v>
+        <v>7025542</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9245,27 +9228,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>I gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9276,6 +9259,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9285,39 +9283,39 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133825717</v>
+        <v>130800371</v>
       </c>
       <c r="B74" t="n">
-        <v>101396</v>
+        <v>78339</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9327,10 +9325,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444683</v>
+        <v>444684</v>
       </c>
       <c r="R74" t="n">
-        <v>7025604</v>
+        <v>7025581</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9357,27 +9355,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På marken längs bäck</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9388,6 +9386,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9397,39 +9410,39 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133825710</v>
+        <v>130800378</v>
       </c>
       <c r="B75" t="n">
-        <v>83334</v>
+        <v>78339</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9439,10 +9452,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444718</v>
+        <v>444675</v>
       </c>
       <c r="R75" t="n">
-        <v>7025467</v>
+        <v>7025530</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9469,27 +9482,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9503,17 +9516,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9524,52 +9537,55 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133825712</v>
+        <v>130800358</v>
       </c>
       <c r="B76" t="n">
-        <v>91967</v>
+        <v>85239</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>229431</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglavshårprick</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Niesslia lobariae</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Etayo &amp; Diederich</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444721</v>
+        <v>444731</v>
       </c>
       <c r="R76" t="n">
-        <v>7025472</v>
+        <v>7025516</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9596,27 +9612,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog med tallöverståndare</t>
+          <t>På död/döende lunglav 1,8 m upp på grov gammal levande sälg (50 cm dbh) i gammal granskog. Mikroskoperad, seta bruna, 75 my långa, 6 my närmare basen gradvis avsmalnande, torra perithecier kollapsade enligt bild i Etayo &amp; Diederich 1996.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9625,22 +9641,27 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>lunglav</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9651,61 +9672,55 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133825705</v>
+        <v>133825703</v>
       </c>
       <c r="B77" t="n">
-        <v>99188</v>
+        <v>79752</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>257107</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>S.Ekman</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444725</v>
+        <v>444737</v>
       </c>
       <c r="R77" t="n">
-        <v>7025449</v>
+        <v>7025451</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9737,7 +9752,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9747,12 +9762,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>32 skott inom 0,7x0,5 m på marken i gammal granskog</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9761,8 +9776,24 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9779,10 +9810,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130800360</v>
+        <v>130800357</v>
       </c>
       <c r="B78" t="n">
-        <v>75454</v>
+        <v>76038</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9790,24 +9821,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1776</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Amerikansk sönderfallslav</t>
-        </is>
+        <v>266100</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Abrothallus diederichii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>Suija &amp; F.Berger</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Litnersmyran, Jmt</t>
@@ -9864,31 +9893,36 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Vid basen av grov gammal levande sälg (50 cm dbh) i gammal granskog</t>
+          <t>På död/döende lunglav 1,8 m upp på grov gammal levande sälg (50 cm dbh) i gammal granskog. Mikroskoperad, sporer 2-4-celliga, delar ibland upp sig redan i asci, ca 4-celliga sporer ca 15x4 my.</t>
         </is>
       </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>lunglav</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 61248-2025 artfynd.xlsx
+++ b/artfynd/A 61248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130812174</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800375</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,6 +1068,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825711</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1165,6 +1185,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330848</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330852</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1404,6 +1434,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800353</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1531,6 +1566,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825708</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1658,6 +1698,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825712</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1785,6 +1830,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800361</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1897,6 +1947,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330845</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2024,6 +2079,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800360</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2136,6 +2196,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330830</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2248,6 +2313,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330835</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2360,6 +2430,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330856</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2472,6 +2547,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330859</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2599,6 +2679,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800356</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2711,6 +2796,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825700</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2823,6 +2913,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825716</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2950,6 +3045,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825713</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3062,6 +3162,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825718</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3174,6 +3279,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330822</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3286,6 +3396,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330824</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3398,6 +3513,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330825</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3510,6 +3630,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330826</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3622,6 +3747,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330831</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3734,6 +3864,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330834</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3846,6 +3981,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330838</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3958,6 +4098,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330839</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4070,6 +4215,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330840</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4182,6 +4332,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330846</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4294,6 +4449,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330854</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4415,6 +4575,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330855</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4536,6 +4701,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330858</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4672,6 +4842,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795187</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4808,6 +4983,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795639</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4944,6 +5124,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800351</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5075,6 +5260,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800352</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5202,6 +5392,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800354</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5329,6 +5524,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800355</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5465,6 +5665,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800367</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5592,6 +5797,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800368</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5728,6 +5938,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800369</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5855,6 +6070,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800372</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5982,6 +6202,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800376</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6094,6 +6319,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330843</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6221,6 +6451,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800359</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6348,6 +6583,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800370</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6475,6 +6715,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800374</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6602,6 +6847,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825710</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6714,6 +6964,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330850</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6826,6 +7081,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330833</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6938,6 +7198,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330827</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7050,6 +7315,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330829</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7162,6 +7432,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330837</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7274,6 +7549,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330857</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7386,6 +7666,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330860</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7513,6 +7798,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795383</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7625,6 +7915,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330836</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7737,6 +8032,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330828</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7864,6 +8164,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800364</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7995,6 +8300,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795562</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8116,6 +8426,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825701</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8237,6 +8552,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825702</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8358,6 +8678,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825705</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8479,6 +8804,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825706</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8600,6 +8930,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825707</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8712,6 +9047,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330823</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8824,6 +9164,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825717</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8936,6 +9281,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825704</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9048,6 +9398,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825714</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9160,6 +9515,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330841</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9287,6 +9647,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800366</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9414,6 +9779,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800371</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9541,6 +9911,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800378</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9676,6 +10051,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800358</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9807,6 +10187,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825703</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9937,8 +10322,92 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130800357</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>